--- a/research/traditional_assets/database/data/bulgaria/bulgaria_advertising.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_advertising.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1244862536613767</v>
+        <v>0.1244022674077153</v>
       </c>
       <c r="C2">
-        <v>10.52782420641262</v>
+        <v>10.43442654146248</v>
       </c>
       <c r="D2">
-        <v>9.24782420641262</v>
+        <v>9.254626541462478</v>
       </c>
       <c r="E2">
-        <v>-5.28</v>
+        <v>-5.1798</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1002</v>
       </c>
       <c r="G2">
         <v>1.28</v>
@@ -1445,28 +1445,28 @@
         <v>1.64</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00504006</v>
       </c>
       <c r="N2">
-        <v>1.64</v>
+        <v>1.63495994</v>
       </c>
       <c r="O2">
-        <v>0.164</v>
+        <v>0.163495994</v>
       </c>
       <c r="P2">
-        <v>1.476</v>
+        <v>1.471463946</v>
       </c>
       <c r="Q2">
-        <v>2.846</v>
+        <v>2.841463946</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1244862536613767</v>
+        <v>0.1252015832401164</v>
       </c>
       <c r="T2">
-        <v>1.217251318914063</v>
+        <v>1.2283172399951</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>325.3929516712102</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1244022674077153</v>
+        <v>0.1243182811540539</v>
       </c>
       <c r="C3">
-        <v>10.43442654146248</v>
+        <v>10.34103889093775</v>
       </c>
       <c r="D3">
-        <v>9.254626541462478</v>
+        <v>9.261438890937747</v>
       </c>
       <c r="E3">
-        <v>-5.1798</v>
+        <v>-5.0796</v>
       </c>
       <c r="F3">
-        <v>0.1002</v>
+        <v>0.2004</v>
       </c>
       <c r="G3">
         <v>1.28</v>
@@ -1527,28 +1527,28 @@
         <v>1.64</v>
       </c>
       <c r="M3">
-        <v>0.00504006</v>
+        <v>0.01008012</v>
       </c>
       <c r="N3">
-        <v>1.63495994</v>
+        <v>1.62991988</v>
       </c>
       <c r="O3">
-        <v>0.163495994</v>
+        <v>0.162991988</v>
       </c>
       <c r="P3">
-        <v>1.471463946</v>
+        <v>1.466927892</v>
       </c>
       <c r="Q3">
-        <v>2.841463946</v>
+        <v>2.836927892</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1252015832401164</v>
+        <v>0.1259315113816876</v>
       </c>
       <c r="T3">
-        <v>1.2283172399951</v>
+        <v>1.239608996200239</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>325.3929516712102</v>
+        <v>162.6964758356051</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1243182811540539</v>
+        <v>0.1242342949003925</v>
       </c>
       <c r="C4">
-        <v>10.34103889093775</v>
+        <v>10.24766127696964</v>
       </c>
       <c r="D4">
-        <v>9.261438890937747</v>
+        <v>9.268261276969636</v>
       </c>
       <c r="E4">
-        <v>-5.0796</v>
+        <v>-4.9794</v>
       </c>
       <c r="F4">
-        <v>0.2004</v>
+        <v>0.3006</v>
       </c>
       <c r="G4">
         <v>1.28</v>
@@ -1609,28 +1609,28 @@
         <v>1.64</v>
       </c>
       <c r="M4">
-        <v>0.01008012</v>
+        <v>0.01512018</v>
       </c>
       <c r="N4">
-        <v>1.62991988</v>
+        <v>1.62487982</v>
       </c>
       <c r="O4">
-        <v>0.162991988</v>
+        <v>0.162487982</v>
       </c>
       <c r="P4">
-        <v>1.466927892</v>
+        <v>1.462391838</v>
       </c>
       <c r="Q4">
-        <v>2.836927892</v>
+        <v>2.832391837999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1259315113816876</v>
+        <v>0.1266764895880335</v>
       </c>
       <c r="T4">
-        <v>1.239608996200239</v>
+        <v>1.251133572120949</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>162.6964758356051</v>
+        <v>108.4643172237367</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1242342949003925</v>
+        <v>0.1241503086467312</v>
       </c>
       <c r="C5">
-        <v>10.24766127696964</v>
+        <v>10.15429372175461</v>
       </c>
       <c r="D5">
-        <v>9.268261276969636</v>
+        <v>9.27509372175461</v>
       </c>
       <c r="E5">
-        <v>-4.9794</v>
+        <v>-4.8792</v>
       </c>
       <c r="F5">
-        <v>0.3006</v>
+        <v>0.4008</v>
       </c>
       <c r="G5">
         <v>1.28</v>
@@ -1691,28 +1691,28 @@
         <v>1.64</v>
       </c>
       <c r="M5">
-        <v>0.01512018</v>
+        <v>0.02016024</v>
       </c>
       <c r="N5">
-        <v>1.62487982</v>
+        <v>1.61983976</v>
       </c>
       <c r="O5">
-        <v>0.162487982</v>
+        <v>0.161983976</v>
       </c>
       <c r="P5">
-        <v>1.462391838</v>
+        <v>1.457855784</v>
       </c>
       <c r="Q5">
-        <v>2.832391837999999</v>
+        <v>2.827855784</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1266764895880335</v>
+        <v>0.1274369881736783</v>
       </c>
       <c r="T5">
-        <v>1.251133572120949</v>
+        <v>1.26289824337334</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>108.4643172237367</v>
+        <v>81.34823791780255</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1241503086467312</v>
+        <v>0.1240663223930698</v>
       </c>
       <c r="C6">
-        <v>10.15429372175461</v>
+        <v>10.06093624755464</v>
       </c>
       <c r="D6">
-        <v>9.27509372175461</v>
+        <v>9.281936247554642</v>
       </c>
       <c r="E6">
-        <v>-4.8792</v>
+        <v>-4.779</v>
       </c>
       <c r="F6">
-        <v>0.4008</v>
+        <v>0.501</v>
       </c>
       <c r="G6">
         <v>1.28</v>
@@ -1773,28 +1773,28 @@
         <v>1.64</v>
       </c>
       <c r="M6">
-        <v>0.02016024</v>
+        <v>0.0252003</v>
       </c>
       <c r="N6">
-        <v>1.61983976</v>
+        <v>1.6147997</v>
       </c>
       <c r="O6">
-        <v>0.161983976</v>
+        <v>0.16147997</v>
       </c>
       <c r="P6">
-        <v>1.457855784</v>
+        <v>1.45331973</v>
       </c>
       <c r="Q6">
-        <v>2.827855784</v>
+        <v>2.82331973</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1274369881736783</v>
+        <v>0.1282134972558629</v>
       </c>
       <c r="T6">
-        <v>1.26289824337334</v>
+        <v>1.274910591915255</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>81.34823791780255</v>
+        <v>65.07859033424204</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1240663223930698</v>
+        <v>0.1239823361394084</v>
       </c>
       <c r="C7">
-        <v>10.06093624755464</v>
+        <v>9.967588876697432</v>
       </c>
       <c r="D7">
-        <v>9.281936247554642</v>
+        <v>9.288788876697433</v>
       </c>
       <c r="E7">
-        <v>-4.779</v>
+        <v>-4.6788</v>
       </c>
       <c r="F7">
-        <v>0.501</v>
+        <v>0.6012000000000001</v>
       </c>
       <c r="G7">
         <v>1.28</v>
@@ -1855,28 +1855,28 @@
         <v>1.64</v>
       </c>
       <c r="M7">
-        <v>0.0252003</v>
+        <v>0.03024036</v>
       </c>
       <c r="N7">
-        <v>1.6147997</v>
+        <v>1.60975964</v>
       </c>
       <c r="O7">
-        <v>0.16147997</v>
+        <v>0.160975964</v>
       </c>
       <c r="P7">
-        <v>1.45331973</v>
+        <v>1.448783676</v>
       </c>
       <c r="Q7">
-        <v>2.82331973</v>
+        <v>2.818783676</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1282134972558629</v>
+        <v>0.1290065278078813</v>
       </c>
       <c r="T7">
-        <v>1.274910591915255</v>
+        <v>1.287178522341041</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>65.07859033424204</v>
+        <v>54.23215861186836</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1239823361394084</v>
+        <v>0.123898349885747</v>
       </c>
       <c r="C8">
-        <v>9.967588876697432</v>
+        <v>9.874251631576685</v>
       </c>
       <c r="D8">
-        <v>9.288788876697433</v>
+        <v>9.295651631576686</v>
       </c>
       <c r="E8">
-        <v>-4.678800000000001</v>
+        <v>-4.578600000000001</v>
       </c>
       <c r="F8">
-        <v>0.6012</v>
+        <v>0.7013999999999999</v>
       </c>
       <c r="G8">
         <v>1.28</v>
@@ -1937,28 +1937,28 @@
         <v>1.64</v>
       </c>
       <c r="M8">
-        <v>0.03024036</v>
+        <v>0.03528041999999999</v>
       </c>
       <c r="N8">
-        <v>1.60975964</v>
+        <v>1.60471958</v>
       </c>
       <c r="O8">
-        <v>0.160975964</v>
+        <v>0.160471958</v>
       </c>
       <c r="P8">
-        <v>1.448783676</v>
+        <v>1.444247622</v>
       </c>
       <c r="Q8">
-        <v>2.818783676</v>
+        <v>2.814247622</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1290065278078813</v>
+        <v>0.1298166127803731</v>
       </c>
       <c r="T8">
-        <v>1.287178522341041</v>
+        <v>1.299710279227596</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>54.23215861186837</v>
+        <v>46.48470738160147</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.123898349885747</v>
+        <v>0.1238143636320857</v>
       </c>
       <c r="C9">
-        <v>9.874251631576684</v>
+        <v>9.780924534652311</v>
       </c>
       <c r="D9">
-        <v>9.295651631576684</v>
+        <v>9.302524534652312</v>
       </c>
       <c r="E9">
-        <v>-4.5786</v>
+        <v>-4.478400000000001</v>
       </c>
       <c r="F9">
-        <v>0.7014</v>
+        <v>0.8016</v>
       </c>
       <c r="G9">
         <v>1.28</v>
@@ -2019,28 +2019,28 @@
         <v>1.64</v>
       </c>
       <c r="M9">
-        <v>0.03528042</v>
+        <v>0.04032048</v>
       </c>
       <c r="N9">
-        <v>1.60471958</v>
+        <v>1.59967952</v>
       </c>
       <c r="O9">
-        <v>0.160471958</v>
+        <v>0.159967952</v>
       </c>
       <c r="P9">
-        <v>1.444247622</v>
+        <v>1.439711568</v>
       </c>
       <c r="Q9">
-        <v>2.814247622</v>
+        <v>2.809711568</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1298166127803732</v>
+        <v>0.1306443082957453</v>
       </c>
       <c r="T9">
-        <v>1.299710279227596</v>
+        <v>1.312514465611685</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>46.48470738160145</v>
+        <v>40.67411895890127</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1238143636320857</v>
+        <v>0.1237303773784243</v>
       </c>
       <c r="C10">
-        <v>9.780924534652311</v>
+        <v>9.687607608450719</v>
       </c>
       <c r="D10">
-        <v>9.302524534652312</v>
+        <v>9.309407608450719</v>
       </c>
       <c r="E10">
-        <v>-4.478400000000001</v>
+        <v>-4.378200000000001</v>
       </c>
       <c r="F10">
-        <v>0.8016</v>
+        <v>0.9017999999999999</v>
       </c>
       <c r="G10">
         <v>1.28</v>
@@ -2101,28 +2101,28 @@
         <v>1.64</v>
       </c>
       <c r="M10">
-        <v>0.04032048</v>
+        <v>0.04536054</v>
       </c>
       <c r="N10">
-        <v>1.59967952</v>
+        <v>1.59463946</v>
       </c>
       <c r="O10">
-        <v>0.159967952</v>
+        <v>0.159463946</v>
       </c>
       <c r="P10">
-        <v>1.439711568</v>
+        <v>1.435175514</v>
       </c>
       <c r="Q10">
-        <v>2.809711568</v>
+        <v>2.805175514</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1306443082957453</v>
+        <v>0.1314901949213453</v>
       </c>
       <c r="T10">
-        <v>1.312514465611685</v>
+        <v>1.325600062685534</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>40.67411895890127</v>
+        <v>36.15477240791225</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1237303773784243</v>
+        <v>0.1236463911247629</v>
       </c>
       <c r="C11">
-        <v>9.687607608450719</v>
+        <v>9.594300875565015</v>
       </c>
       <c r="D11">
-        <v>9.309407608450719</v>
+        <v>9.316300875565014</v>
       </c>
       <c r="E11">
-        <v>-4.378200000000001</v>
+        <v>-4.278</v>
       </c>
       <c r="F11">
-        <v>0.9017999999999999</v>
+        <v>1.002</v>
       </c>
       <c r="G11">
         <v>1.28</v>
@@ -2183,28 +2183,28 @@
         <v>1.64</v>
       </c>
       <c r="M11">
-        <v>0.04536054</v>
+        <v>0.05040059999999999</v>
       </c>
       <c r="N11">
-        <v>1.59463946</v>
+        <v>1.5895994</v>
       </c>
       <c r="O11">
-        <v>0.159463946</v>
+        <v>0.15895994</v>
       </c>
       <c r="P11">
-        <v>1.435175514</v>
+        <v>1.43063946</v>
       </c>
       <c r="Q11">
-        <v>2.805175514</v>
+        <v>2.80063946</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1314901949213453</v>
+        <v>0.1323548790275143</v>
       </c>
       <c r="T11">
-        <v>1.325600062685534</v>
+        <v>1.338976450805469</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>36.15477240791225</v>
+        <v>32.53929516712103</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1236463911247629</v>
+        <v>0.1235624048711015</v>
       </c>
       <c r="C12">
-        <v>9.594300875565013</v>
+        <v>9.501004358655289</v>
       </c>
       <c r="D12">
-        <v>9.316300875565014</v>
+        <v>9.323204358655289</v>
       </c>
       <c r="E12">
-        <v>-4.278</v>
+        <v>-4.1778</v>
       </c>
       <c r="F12">
-        <v>1.002</v>
+        <v>1.1022</v>
       </c>
       <c r="G12">
         <v>1.28</v>
@@ -2265,28 +2265,28 @@
         <v>1.64</v>
       </c>
       <c r="M12">
-        <v>0.0504006</v>
+        <v>0.05544066</v>
       </c>
       <c r="N12">
-        <v>1.5895994</v>
+        <v>1.58455934</v>
       </c>
       <c r="O12">
-        <v>0.15895994</v>
+        <v>0.158455934</v>
       </c>
       <c r="P12">
-        <v>1.43063946</v>
+        <v>1.426103406</v>
       </c>
       <c r="Q12">
-        <v>2.80063946</v>
+        <v>2.796103406</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1323548790275143</v>
+        <v>0.1332389942371927</v>
       </c>
       <c r="T12">
-        <v>1.338976450805469</v>
+        <v>1.352653431916863</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.53929516712103</v>
+        <v>29.58117742465547</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1235624048711015</v>
+        <v>0.1234784186174401</v>
       </c>
       <c r="C13">
-        <v>9.501004358655289</v>
+        <v>9.407718080448834</v>
       </c>
       <c r="D13">
-        <v>9.323204358655289</v>
+        <v>9.330118080448834</v>
       </c>
       <c r="E13">
-        <v>-4.1778</v>
+        <v>-4.0776</v>
       </c>
       <c r="F13">
-        <v>1.1022</v>
+        <v>1.2024</v>
       </c>
       <c r="G13">
         <v>1.28</v>
@@ -2347,28 +2347,28 @@
         <v>1.64</v>
       </c>
       <c r="M13">
-        <v>0.05544066</v>
+        <v>0.06048071999999999</v>
       </c>
       <c r="N13">
-        <v>1.58455934</v>
+        <v>1.57951928</v>
       </c>
       <c r="O13">
-        <v>0.158455934</v>
+        <v>0.157951928</v>
       </c>
       <c r="P13">
-        <v>1.426103406</v>
+        <v>1.421567352</v>
       </c>
       <c r="Q13">
-        <v>2.796103406</v>
+        <v>2.791567352</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1332389942371927</v>
+        <v>0.1341432029743638</v>
       </c>
       <c r="T13">
-        <v>1.352653431916863</v>
+        <v>1.366641253508061</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.58117742465547</v>
+        <v>27.11607930593419</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1234784186174401</v>
+        <v>0.1233944323637788</v>
       </c>
       <c r="C14">
-        <v>9.407718080448834</v>
+        <v>9.314442063740415</v>
       </c>
       <c r="D14">
-        <v>9.330118080448834</v>
+        <v>9.337042063740416</v>
       </c>
       <c r="E14">
-        <v>-4.0776</v>
+        <v>-3.9774</v>
       </c>
       <c r="F14">
-        <v>1.2024</v>
+        <v>1.3026</v>
       </c>
       <c r="G14">
         <v>1.28</v>
@@ -2429,28 +2429,28 @@
         <v>1.64</v>
       </c>
       <c r="M14">
-        <v>0.06048071999999999</v>
+        <v>0.06552078</v>
       </c>
       <c r="N14">
-        <v>1.57951928</v>
+        <v>1.57447922</v>
       </c>
       <c r="O14">
-        <v>0.157951928</v>
+        <v>0.157447922</v>
       </c>
       <c r="P14">
-        <v>1.421567352</v>
+        <v>1.417031298</v>
       </c>
       <c r="Q14">
-        <v>2.791567352</v>
+        <v>2.787031298</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1341432029743638</v>
+        <v>0.1350681981192859</v>
       </c>
       <c r="T14">
-        <v>1.366641253508061</v>
+        <v>1.380950634216299</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.11607930593419</v>
+        <v>25.03022705163156</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1233944323637788</v>
+        <v>0.1233104461101174</v>
       </c>
       <c r="C15">
-        <v>9.314442063740415</v>
+        <v>9.221176331392513</v>
       </c>
       <c r="D15">
-        <v>9.337042063740416</v>
+        <v>9.343976331392515</v>
       </c>
       <c r="E15">
-        <v>-3.9774</v>
+        <v>-3.8772</v>
       </c>
       <c r="F15">
-        <v>1.3026</v>
+        <v>1.4028</v>
       </c>
       <c r="G15">
         <v>1.28</v>
@@ -2511,28 +2511,28 @@
         <v>1.64</v>
       </c>
       <c r="M15">
-        <v>0.06552078</v>
+        <v>0.07056084</v>
       </c>
       <c r="N15">
-        <v>1.57447922</v>
+        <v>1.56943916</v>
       </c>
       <c r="O15">
-        <v>0.157447922</v>
+        <v>0.156943916</v>
       </c>
       <c r="P15">
-        <v>1.417031298</v>
+        <v>1.412495244</v>
       </c>
       <c r="Q15">
-        <v>2.787031298</v>
+        <v>2.782495244</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1350681981192859</v>
+        <v>0.1360147047792062</v>
       </c>
       <c r="T15">
-        <v>1.380950634216299</v>
+        <v>1.395592791220077</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.03022705163156</v>
+        <v>23.24235369080073</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1233104461101174</v>
+        <v>0.123226459856456</v>
       </c>
       <c r="C16">
-        <v>9.221176331392513</v>
+        <v>9.127920906335568</v>
       </c>
       <c r="D16">
-        <v>9.343976331392515</v>
+        <v>9.350920906335569</v>
       </c>
       <c r="E16">
-        <v>-3.8772</v>
+        <v>-3.777</v>
       </c>
       <c r="F16">
-        <v>1.4028</v>
+        <v>1.503</v>
       </c>
       <c r="G16">
         <v>1.28</v>
@@ -2593,28 +2593,28 @@
         <v>1.64</v>
       </c>
       <c r="M16">
-        <v>0.07056084</v>
+        <v>0.0756009</v>
       </c>
       <c r="N16">
-        <v>1.56943916</v>
+        <v>1.5643991</v>
       </c>
       <c r="O16">
-        <v>0.156943916</v>
+        <v>0.15643991</v>
       </c>
       <c r="P16">
-        <v>1.412495244</v>
+        <v>1.40795919</v>
       </c>
       <c r="Q16">
-        <v>2.782495244</v>
+        <v>2.77795919</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1360147047792062</v>
+        <v>0.1369834821840659</v>
       </c>
       <c r="T16">
-        <v>1.395592791220077</v>
+        <v>1.41057946956512</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.24235369080073</v>
+        <v>21.69286344474735</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.123226459856456</v>
+        <v>0.1231424736027946</v>
       </c>
       <c r="C17">
-        <v>9.127920906335568</v>
+        <v>9.034675811568249</v>
       </c>
       <c r="D17">
-        <v>9.350920906335569</v>
+        <v>9.357875811568249</v>
       </c>
       <c r="E17">
-        <v>-3.777</v>
+        <v>-3.6768</v>
       </c>
       <c r="F17">
-        <v>1.503</v>
+        <v>1.6032</v>
       </c>
       <c r="G17">
         <v>1.28</v>
@@ -2675,28 +2675,28 @@
         <v>1.64</v>
       </c>
       <c r="M17">
-        <v>0.07560089999999998</v>
+        <v>0.08064096</v>
       </c>
       <c r="N17">
-        <v>1.5643991</v>
+        <v>1.55935904</v>
       </c>
       <c r="O17">
-        <v>0.15643991</v>
+        <v>0.155935904</v>
       </c>
       <c r="P17">
-        <v>1.40795919</v>
+        <v>1.403423136</v>
       </c>
       <c r="Q17">
-        <v>2.77795919</v>
+        <v>2.773423136</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1369834821840659</v>
+        <v>0.1379753257176127</v>
       </c>
       <c r="T17">
-        <v>1.41057946956512</v>
+        <v>1.425922973585045</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.69286344474735</v>
+        <v>20.33705947945064</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1231424736027946</v>
+        <v>0.1230584873491332</v>
       </c>
       <c r="C18">
-        <v>9.034675811568249</v>
+        <v>8.941441070157696</v>
       </c>
       <c r="D18">
-        <v>9.357875811568249</v>
+        <v>9.364841070157697</v>
       </c>
       <c r="E18">
-        <v>-3.6768</v>
+        <v>-3.5766</v>
       </c>
       <c r="F18">
-        <v>1.6032</v>
+        <v>1.7034</v>
       </c>
       <c r="G18">
         <v>1.28</v>
@@ -2757,28 +2757,28 @@
         <v>1.64</v>
       </c>
       <c r="M18">
-        <v>0.08064096</v>
+        <v>0.08568102</v>
       </c>
       <c r="N18">
-        <v>1.55935904</v>
+        <v>1.55431898</v>
       </c>
       <c r="O18">
-        <v>0.155935904</v>
+        <v>0.155431898</v>
       </c>
       <c r="P18">
-        <v>1.403423136</v>
+        <v>1.398887082</v>
       </c>
       <c r="Q18">
-        <v>2.773423136</v>
+        <v>2.768887082</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1379753257176127</v>
+        <v>0.1389910690953413</v>
       </c>
       <c r="T18">
-        <v>1.425922973585045</v>
+        <v>1.441636200593402</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.33705947945064</v>
+        <v>19.14076186301237</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1230584873491332</v>
+        <v>0.1229745010954719</v>
       </c>
       <c r="C19">
-        <v>8.941441070157696</v>
+        <v>8.84821670523977</v>
       </c>
       <c r="D19">
-        <v>9.364841070157697</v>
+        <v>9.37181670523977</v>
       </c>
       <c r="E19">
-        <v>-3.5766</v>
+        <v>-3.4764</v>
       </c>
       <c r="F19">
-        <v>1.7034</v>
+        <v>1.8036</v>
       </c>
       <c r="G19">
         <v>1.28</v>
@@ -2839,28 +2839,28 @@
         <v>1.64</v>
       </c>
       <c r="M19">
-        <v>0.08568102</v>
+        <v>0.09072108</v>
       </c>
       <c r="N19">
-        <v>1.55431898</v>
+        <v>1.54927892</v>
       </c>
       <c r="O19">
-        <v>0.155431898</v>
+        <v>0.154927892</v>
       </c>
       <c r="P19">
-        <v>1.398887082</v>
+        <v>1.394351028</v>
       </c>
       <c r="Q19">
-        <v>2.768887082</v>
+        <v>2.764351028</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1389910690953413</v>
+        <v>0.140031586701795</v>
       </c>
       <c r="T19">
-        <v>1.441636200593402</v>
+        <v>1.457732677040987</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.14076186301237</v>
+        <v>18.07738620395612</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1229745010954719</v>
+        <v>0.1228905148418105</v>
       </c>
       <c r="C20">
-        <v>8.84821670523977</v>
+        <v>8.755002740019323</v>
       </c>
       <c r="D20">
-        <v>9.37181670523977</v>
+        <v>9.378802740019324</v>
       </c>
       <c r="E20">
-        <v>-3.4764</v>
+        <v>-3.3762</v>
       </c>
       <c r="F20">
-        <v>1.8036</v>
+        <v>1.9038</v>
       </c>
       <c r="G20">
         <v>1.28</v>
@@ -2921,28 +2921,28 @@
         <v>1.64</v>
       </c>
       <c r="M20">
-        <v>0.09072108</v>
+        <v>0.09576113999999999</v>
       </c>
       <c r="N20">
-        <v>1.54927892</v>
+        <v>1.54423886</v>
       </c>
       <c r="O20">
-        <v>0.154927892</v>
+        <v>0.154423886</v>
       </c>
       <c r="P20">
-        <v>1.394351028</v>
+        <v>1.389814974</v>
       </c>
       <c r="Q20">
-        <v>2.764351028</v>
+        <v>2.759814974</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.140031586701795</v>
+        <v>0.1410977961010006</v>
       </c>
       <c r="T20">
-        <v>1.457732677040987</v>
+        <v>1.474226597351476</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.07738620395612</v>
+        <v>17.12594482480054</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1228905148418105</v>
+        <v>0.1228065285881492</v>
       </c>
       <c r="C21">
-        <v>8.755002740019323</v>
+        <v>8.661799197770453</v>
       </c>
       <c r="D21">
-        <v>9.378802740019324</v>
+        <v>9.385799197770453</v>
       </c>
       <c r="E21">
-        <v>-3.3762</v>
+        <v>-3.276</v>
       </c>
       <c r="F21">
-        <v>1.9038</v>
+        <v>2.004</v>
       </c>
       <c r="G21">
         <v>1.28</v>
@@ -3003,28 +3003,28 @@
         <v>1.64</v>
       </c>
       <c r="M21">
-        <v>0.09576113999999999</v>
+        <v>0.1008012</v>
       </c>
       <c r="N21">
-        <v>1.54423886</v>
+        <v>1.5391988</v>
       </c>
       <c r="O21">
-        <v>0.154423886</v>
+        <v>0.15391988</v>
       </c>
       <c r="P21">
-        <v>1.389814974</v>
+        <v>1.38527892</v>
       </c>
       <c r="Q21">
-        <v>2.759814974</v>
+        <v>2.75527892</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1410977961010006</v>
+        <v>0.1421906607351864</v>
       </c>
       <c r="T21">
-        <v>1.474226597351476</v>
+        <v>1.491132865669727</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.12594482480054</v>
+        <v>16.26964758356051</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1228065285881492</v>
+        <v>0.1227225423344877</v>
       </c>
       <c r="C22">
-        <v>8.661799197770453</v>
+        <v>8.568606101836759</v>
       </c>
       <c r="D22">
-        <v>9.385799197770453</v>
+        <v>9.39280610183676</v>
       </c>
       <c r="E22">
-        <v>-3.276</v>
+        <v>-3.1758</v>
       </c>
       <c r="F22">
-        <v>2.004</v>
+        <v>2.1042</v>
       </c>
       <c r="G22">
         <v>1.28</v>
@@ -3085,28 +3085,28 @@
         <v>1.64</v>
       </c>
       <c r="M22">
-        <v>0.1008012</v>
+        <v>0.10584126</v>
       </c>
       <c r="N22">
-        <v>1.5391988</v>
+        <v>1.53415874</v>
       </c>
       <c r="O22">
-        <v>0.15391988</v>
+        <v>0.153415874</v>
       </c>
       <c r="P22">
-        <v>1.38527892</v>
+        <v>1.380742866</v>
       </c>
       <c r="Q22">
-        <v>2.75527892</v>
+        <v>2.750742866</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1421906607351864</v>
+        <v>0.1433111928284655</v>
       </c>
       <c r="T22">
-        <v>1.491132865669727</v>
+        <v>1.508467140780845</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.26964758356051</v>
+        <v>15.49490246053382</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1227225423344877</v>
+        <v>0.1226385560808264</v>
       </c>
       <c r="C23">
-        <v>8.56860610183676</v>
+        <v>8.475423475631581</v>
       </c>
       <c r="D23">
-        <v>9.39280610183676</v>
+        <v>9.399823475631582</v>
       </c>
       <c r="E23">
-        <v>-3.175800000000001</v>
+        <v>-3.0756</v>
       </c>
       <c r="F23">
-        <v>2.1042</v>
+        <v>2.2044</v>
       </c>
       <c r="G23">
         <v>1.28</v>
@@ -3167,28 +3167,28 @@
         <v>1.64</v>
       </c>
       <c r="M23">
-        <v>0.10584126</v>
+        <v>0.11088132</v>
       </c>
       <c r="N23">
-        <v>1.53415874</v>
+        <v>1.52911868</v>
       </c>
       <c r="O23">
-        <v>0.153415874</v>
+        <v>0.152911868</v>
       </c>
       <c r="P23">
-        <v>1.380742866</v>
+        <v>1.376206812</v>
       </c>
       <c r="Q23">
-        <v>2.750742866</v>
+        <v>2.746206812</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1433111928284655</v>
+        <v>0.14446045651388</v>
       </c>
       <c r="T23">
-        <v>1.508467140780845</v>
+        <v>1.526245884484556</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.49490246053382</v>
+        <v>14.79058871232774</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1226385560808264</v>
+        <v>0.122554569827165</v>
       </c>
       <c r="C24">
-        <v>8.475423475631581</v>
+        <v>8.382251342638298</v>
       </c>
       <c r="D24">
-        <v>9.399823475631582</v>
+        <v>9.4068513426383</v>
       </c>
       <c r="E24">
-        <v>-3.0756</v>
+        <v>-2.9754</v>
       </c>
       <c r="F24">
-        <v>2.2044</v>
+        <v>2.3046</v>
       </c>
       <c r="G24">
         <v>1.28</v>
@@ -3249,28 +3249,28 @@
         <v>1.64</v>
       </c>
       <c r="M24">
-        <v>0.11088132</v>
+        <v>0.11592138</v>
       </c>
       <c r="N24">
-        <v>1.52911868</v>
+        <v>1.52407862</v>
       </c>
       <c r="O24">
-        <v>0.152911868</v>
+        <v>0.152407862</v>
       </c>
       <c r="P24">
-        <v>1.376206812</v>
+        <v>1.371670758</v>
       </c>
       <c r="Q24">
-        <v>2.746206812</v>
+        <v>2.741670758</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.14446045651388</v>
+        <v>0.1456395712041104</v>
       </c>
       <c r="T24">
-        <v>1.526245884484556</v>
+        <v>1.544486413739012</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.79058871232774</v>
+        <v>14.1475196378787</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.122554569827165</v>
+        <v>0.1224705835735036</v>
       </c>
       <c r="C25">
-        <v>8.382251342638298</v>
+        <v>8.289089726410577</v>
       </c>
       <c r="D25">
-        <v>9.4068513426383</v>
+        <v>9.413889726410577</v>
       </c>
       <c r="E25">
-        <v>-2.9754</v>
+        <v>-2.8752</v>
       </c>
       <c r="F25">
-        <v>2.3046</v>
+        <v>2.4048</v>
       </c>
       <c r="G25">
         <v>1.28</v>
@@ -3331,28 +3331,28 @@
         <v>1.64</v>
       </c>
       <c r="M25">
-        <v>0.11592138</v>
+        <v>0.12096144</v>
       </c>
       <c r="N25">
-        <v>1.52407862</v>
+        <v>1.51903856</v>
       </c>
       <c r="O25">
-        <v>0.152407862</v>
+        <v>0.151903856</v>
       </c>
       <c r="P25">
-        <v>1.371670758</v>
+        <v>1.367134704</v>
       </c>
       <c r="Q25">
-        <v>2.741670758</v>
+        <v>2.737134704</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1456395712041104</v>
+        <v>0.1468497152282942</v>
       </c>
       <c r="T25">
-        <v>1.544486413739012</v>
+        <v>1.563206956921217</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.1475196378787</v>
+        <v>13.55803965296709</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1224705835735036</v>
+        <v>0.1223865973198422</v>
       </c>
       <c r="C26">
-        <v>8.289089726410577</v>
+        <v>8.195938650572611</v>
       </c>
       <c r="D26">
-        <v>9.413889726410577</v>
+        <v>9.420938650572612</v>
       </c>
       <c r="E26">
-        <v>-2.8752</v>
+        <v>-2.775</v>
       </c>
       <c r="F26">
-        <v>2.4048</v>
+        <v>2.505</v>
       </c>
       <c r="G26">
         <v>1.28</v>
@@ -3413,28 +3413,28 @@
         <v>1.64</v>
       </c>
       <c r="M26">
-        <v>0.12096144</v>
+        <v>0.1260015</v>
       </c>
       <c r="N26">
-        <v>1.51903856</v>
+        <v>1.5139985</v>
       </c>
       <c r="O26">
-        <v>0.151903856</v>
+        <v>0.15139985</v>
       </c>
       <c r="P26">
-        <v>1.367134704</v>
+        <v>1.36259865</v>
       </c>
       <c r="Q26">
-        <v>2.737134704</v>
+        <v>2.73259865</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1468497152282942</v>
+        <v>0.1480921297597897</v>
       </c>
       <c r="T26">
-        <v>1.563206956921217</v>
+        <v>1.582426714588282</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.55803965296709</v>
+        <v>13.01571806684841</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1223865973198422</v>
+        <v>0.1226536110661809</v>
       </c>
       <c r="C27">
-        <v>8.195938650572611</v>
+        <v>8.073364802615201</v>
       </c>
       <c r="D27">
-        <v>9.420938650572612</v>
+        <v>9.398564802615201</v>
       </c>
       <c r="E27">
-        <v>-2.775</v>
+        <v>-2.6748</v>
       </c>
       <c r="F27">
-        <v>2.505</v>
+        <v>2.6052</v>
       </c>
       <c r="G27">
         <v>1.28</v>
@@ -3495,45 +3495,45 @@
         <v>1.64</v>
       </c>
       <c r="M27">
-        <v>0.1260015</v>
+        <v>0.13494936</v>
       </c>
       <c r="N27">
-        <v>1.5139985</v>
+        <v>1.50505064</v>
       </c>
       <c r="O27">
-        <v>0.15139985</v>
+        <v>0.150505064</v>
       </c>
       <c r="P27">
-        <v>1.36259865</v>
+        <v>1.354545576</v>
       </c>
       <c r="Q27">
-        <v>2.73259865</v>
+        <v>2.724545576</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1480921297597897</v>
+        <v>0.1493681230624066</v>
       </c>
       <c r="T27">
-        <v>1.582426714588282</v>
+        <v>1.602165925165266</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.1</v>
       </c>
       <c r="W27">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>13.01571806684841</v>
+        <v>12.1527067634852</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1226536110661809</v>
+        <v>0.1225831248125195</v>
       </c>
       <c r="C28">
-        <v>8.073364802615201</v>
+        <v>7.979060717588909</v>
       </c>
       <c r="D28">
-        <v>9.398564802615201</v>
+        <v>9.404460717588909</v>
       </c>
       <c r="E28">
-        <v>-2.6748</v>
+        <v>-2.5746</v>
       </c>
       <c r="F28">
-        <v>2.6052</v>
+        <v>2.7054</v>
       </c>
       <c r="G28">
         <v>1.28</v>
@@ -3577,28 +3577,28 @@
         <v>1.64</v>
       </c>
       <c r="M28">
-        <v>0.13494936</v>
+        <v>0.14013972</v>
       </c>
       <c r="N28">
-        <v>1.50505064</v>
+        <v>1.49986028</v>
       </c>
       <c r="O28">
-        <v>0.150505064</v>
+        <v>0.149986028</v>
       </c>
       <c r="P28">
-        <v>1.354545576</v>
+        <v>1.349874252</v>
       </c>
       <c r="Q28">
-        <v>2.724545576</v>
+        <v>2.719874251999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1493681230624066</v>
+        <v>0.1506790750856432</v>
       </c>
       <c r="T28">
-        <v>1.602165925165266</v>
+        <v>1.622445936032032</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.1527067634852</v>
+        <v>11.70260651298575</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1225831248125195</v>
+        <v>0.1225126385588581</v>
       </c>
       <c r="C29">
-        <v>7.979060717588909</v>
+        <v>7.884764034465906</v>
       </c>
       <c r="D29">
-        <v>9.404460717588909</v>
+        <v>9.410364034465907</v>
       </c>
       <c r="E29">
-        <v>-2.5746</v>
+        <v>-2.4744</v>
       </c>
       <c r="F29">
-        <v>2.7054</v>
+        <v>2.8056</v>
       </c>
       <c r="G29">
         <v>1.28</v>
@@ -3659,28 +3659,28 @@
         <v>1.64</v>
       </c>
       <c r="M29">
-        <v>0.14013972</v>
+        <v>0.14533008</v>
       </c>
       <c r="N29">
-        <v>1.49986028</v>
+        <v>1.49466992</v>
       </c>
       <c r="O29">
-        <v>0.149986028</v>
+        <v>0.149466992</v>
       </c>
       <c r="P29">
-        <v>1.349874252</v>
+        <v>1.345202928</v>
       </c>
       <c r="Q29">
-        <v>2.719874251999999</v>
+        <v>2.715202928</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1506790750856432</v>
+        <v>0.1520264424428585</v>
       </c>
       <c r="T29">
-        <v>1.622445936032032</v>
+        <v>1.643289280533985</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.70260651298575</v>
+        <v>11.28465628037912</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1225126385588581</v>
+        <v>0.1224421523051967</v>
       </c>
       <c r="C30">
-        <v>7.884764034465906</v>
+        <v>7.790474767193802</v>
       </c>
       <c r="D30">
-        <v>9.410364034465907</v>
+        <v>9.416274767193803</v>
       </c>
       <c r="E30">
-        <v>-2.4744</v>
+        <v>-2.3742</v>
       </c>
       <c r="F30">
-        <v>2.8056</v>
+        <v>2.9058</v>
       </c>
       <c r="G30">
         <v>1.28</v>
@@ -3741,28 +3741,28 @@
         <v>1.64</v>
       </c>
       <c r="M30">
-        <v>0.14533008</v>
+        <v>0.15052044</v>
       </c>
       <c r="N30">
-        <v>1.49466992</v>
+        <v>1.48947956</v>
       </c>
       <c r="O30">
-        <v>0.149466992</v>
+        <v>0.148947956</v>
       </c>
       <c r="P30">
-        <v>1.345202928</v>
+        <v>1.340531604</v>
       </c>
       <c r="Q30">
-        <v>2.715202928</v>
+        <v>2.710531604</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1520264424428585</v>
+        <v>0.1534117638101363</v>
       </c>
       <c r="T30">
-        <v>1.643289280533985</v>
+        <v>1.664719761500782</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.28465628037912</v>
+        <v>10.89553020174536</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1224421523051967</v>
+        <v>0.1223716660515353</v>
       </c>
       <c r="C31">
-        <v>7.790474767193803</v>
+        <v>7.696192929755259</v>
       </c>
       <c r="D31">
-        <v>9.416274767193803</v>
+        <v>9.42219292975526</v>
       </c>
       <c r="E31">
-        <v>-2.374200000000001</v>
+        <v>-2.274</v>
       </c>
       <c r="F31">
-        <v>2.9058</v>
+        <v>3.006</v>
       </c>
       <c r="G31">
         <v>1.28</v>
@@ -3823,28 +3823,28 @@
         <v>1.64</v>
       </c>
       <c r="M31">
-        <v>0.15052044</v>
+        <v>0.1557108</v>
       </c>
       <c r="N31">
-        <v>1.48947956</v>
+        <v>1.4842892</v>
       </c>
       <c r="O31">
-        <v>0.148947956</v>
+        <v>0.14842892</v>
       </c>
       <c r="P31">
-        <v>1.340531604</v>
+        <v>1.33586028</v>
       </c>
       <c r="Q31">
-        <v>2.710531604</v>
+        <v>2.70586028</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1534117638101362</v>
+        <v>0.1548366657879076</v>
       </c>
       <c r="T31">
-        <v>1.664719761500782</v>
+        <v>1.686762541923773</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.89553020174536</v>
+        <v>10.53234586168718</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1223716660515353</v>
+        <v>0.122301179797874</v>
       </c>
       <c r="C32">
-        <v>7.696192929755259</v>
+        <v>7.601918536168114</v>
       </c>
       <c r="D32">
-        <v>9.42219292975526</v>
+        <v>9.428118536168114</v>
       </c>
       <c r="E32">
-        <v>-2.274</v>
+        <v>-2.1738</v>
       </c>
       <c r="F32">
-        <v>3.006</v>
+        <v>3.1062</v>
       </c>
       <c r="G32">
         <v>1.28</v>
@@ -3905,28 +3905,28 @@
         <v>1.64</v>
       </c>
       <c r="M32">
-        <v>0.1557108</v>
+        <v>0.16090116</v>
       </c>
       <c r="N32">
-        <v>1.4842892</v>
+        <v>1.47909884</v>
       </c>
       <c r="O32">
-        <v>0.14842892</v>
+        <v>0.147909884</v>
       </c>
       <c r="P32">
-        <v>1.33586028</v>
+        <v>1.331188956</v>
       </c>
       <c r="Q32">
-        <v>2.70586028</v>
+        <v>2.701188956</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1548366657879076</v>
+        <v>0.1563028692722812</v>
       </c>
       <c r="T32">
-        <v>1.686762541923773</v>
+        <v>1.709444243518445</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.53234586168718</v>
+        <v>10.19259276937469</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.122301179797874</v>
+        <v>0.1222306935442126</v>
       </c>
       <c r="C33">
-        <v>7.601918536168114</v>
+        <v>7.507651600485499</v>
       </c>
       <c r="D33">
-        <v>9.428118536168114</v>
+        <v>9.4340516004855</v>
       </c>
       <c r="E33">
-        <v>-2.1738</v>
+        <v>-2.0736</v>
       </c>
       <c r="F33">
-        <v>3.1062</v>
+        <v>3.2064</v>
       </c>
       <c r="G33">
         <v>1.28</v>
@@ -3987,28 +3987,28 @@
         <v>1.64</v>
       </c>
       <c r="M33">
-        <v>0.16090116</v>
+        <v>0.16609152</v>
       </c>
       <c r="N33">
-        <v>1.47909884</v>
+        <v>1.47390848</v>
       </c>
       <c r="O33">
-        <v>0.147909884</v>
+        <v>0.147390848</v>
       </c>
       <c r="P33">
-        <v>1.331188956</v>
+        <v>1.326517632</v>
       </c>
       <c r="Q33">
-        <v>2.701188956</v>
+        <v>2.696517632</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1563028692722812</v>
+        <v>0.157812196388548</v>
       </c>
       <c r="T33">
-        <v>1.709444243518445</v>
+        <v>1.732793053983548</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.19259276937469</v>
+        <v>9.874074245331729</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1222306935442126</v>
+        <v>0.1226651072905512</v>
       </c>
       <c r="C34">
-        <v>7.507651600485499</v>
+        <v>7.371003886994652</v>
       </c>
       <c r="D34">
-        <v>9.4340516004855</v>
+        <v>9.397603886994652</v>
       </c>
       <c r="E34">
-        <v>-2.0736</v>
+        <v>-1.9734</v>
       </c>
       <c r="F34">
-        <v>3.2064</v>
+        <v>3.3066</v>
       </c>
       <c r="G34">
         <v>1.28</v>
@@ -4069,45 +4069,45 @@
         <v>1.64</v>
       </c>
       <c r="M34">
-        <v>0.16609152</v>
+        <v>0.1769031</v>
       </c>
       <c r="N34">
-        <v>1.47390848</v>
+        <v>1.4630969</v>
       </c>
       <c r="O34">
-        <v>0.147390848</v>
+        <v>0.14630969</v>
       </c>
       <c r="P34">
-        <v>1.326517632</v>
+        <v>1.31678721</v>
       </c>
       <c r="Q34">
-        <v>2.696517632</v>
+        <v>2.686787209999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.157812196388548</v>
+        <v>0.1593665780455988</v>
       </c>
       <c r="T34">
-        <v>1.732793053983548</v>
+        <v>1.75683884386552</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.1</v>
       </c>
       <c r="W34">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>9.874074245331729</v>
+        <v>9.270611990406044</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1226651072905512</v>
+        <v>0.1226099210368898</v>
       </c>
       <c r="C35">
-        <v>7.371003886994652</v>
+        <v>7.275418440984211</v>
       </c>
       <c r="D35">
-        <v>9.397603886994652</v>
+        <v>9.402218440984212</v>
       </c>
       <c r="E35">
-        <v>-1.9734</v>
+        <v>-1.8732</v>
       </c>
       <c r="F35">
-        <v>3.3066</v>
+        <v>3.4068</v>
       </c>
       <c r="G35">
         <v>1.28</v>
@@ -4151,28 +4151,28 @@
         <v>1.64</v>
       </c>
       <c r="M35">
-        <v>0.1769031</v>
+        <v>0.1822638</v>
       </c>
       <c r="N35">
-        <v>1.4630969</v>
+        <v>1.4577362</v>
       </c>
       <c r="O35">
-        <v>0.14630969</v>
+        <v>0.14577362</v>
       </c>
       <c r="P35">
-        <v>1.31678721</v>
+        <v>1.31196258</v>
       </c>
       <c r="Q35">
-        <v>2.686787209999999</v>
+        <v>2.68196258</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1593665780455988</v>
+        <v>0.1609680621771059</v>
       </c>
       <c r="T35">
-        <v>1.75683884386552</v>
+        <v>1.781613294046947</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.270611990406044</v>
+        <v>8.997946931864689</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1226099210368898</v>
+        <v>0.1225547347832285</v>
       </c>
       <c r="C36">
-        <v>7.275418440984211</v>
+        <v>7.179837529016723</v>
       </c>
       <c r="D36">
-        <v>9.402218440984212</v>
+        <v>9.406837529016723</v>
       </c>
       <c r="E36">
-        <v>-1.8732</v>
+        <v>-1.773</v>
       </c>
       <c r="F36">
-        <v>3.4068</v>
+        <v>3.507</v>
       </c>
       <c r="G36">
         <v>1.28</v>
@@ -4233,28 +4233,28 @@
         <v>1.64</v>
       </c>
       <c r="M36">
-        <v>0.1822638</v>
+        <v>0.1876245</v>
       </c>
       <c r="N36">
-        <v>1.4577362</v>
+        <v>1.4523755</v>
       </c>
       <c r="O36">
-        <v>0.14577362</v>
+        <v>0.14523755</v>
       </c>
       <c r="P36">
-        <v>1.31196258</v>
+        <v>1.30713795</v>
       </c>
       <c r="Q36">
-        <v>2.68196258</v>
+        <v>2.67713795</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1609680621771059</v>
+        <v>0.1626188227434284</v>
       </c>
       <c r="T36">
-        <v>1.781613294046947</v>
+        <v>1.807150035003185</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.997946931864689</v>
+        <v>8.740862733811413</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1225547347832285</v>
+        <v>0.1224995485295671</v>
       </c>
       <c r="C37">
-        <v>7.179837529016723</v>
+        <v>7.084261157777863</v>
       </c>
       <c r="D37">
-        <v>9.406837529016723</v>
+        <v>9.411461157777865</v>
       </c>
       <c r="E37">
-        <v>-1.773</v>
+        <v>-1.6728</v>
       </c>
       <c r="F37">
-        <v>3.507</v>
+        <v>3.6072</v>
       </c>
       <c r="G37">
         <v>1.28</v>
@@ -4315,28 +4315,28 @@
         <v>1.64</v>
       </c>
       <c r="M37">
-        <v>0.1876245</v>
+        <v>0.1929852</v>
       </c>
       <c r="N37">
-        <v>1.4523755</v>
+        <v>1.4470148</v>
       </c>
       <c r="O37">
-        <v>0.14523755</v>
+        <v>0.14470148</v>
       </c>
       <c r="P37">
-        <v>1.30713795</v>
+        <v>1.30231332</v>
       </c>
       <c r="Q37">
-        <v>2.67713795</v>
+        <v>2.67231332</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1626188227434284</v>
+        <v>0.1643211695774486</v>
       </c>
       <c r="T37">
-        <v>1.807150035003185</v>
+        <v>1.833484799114307</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.740862733811413</v>
+        <v>8.498060991205541</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1224995485295671</v>
+        <v>0.1224443622759057</v>
       </c>
       <c r="C38">
-        <v>7.084261157777864</v>
+        <v>6.988689333966491</v>
       </c>
       <c r="D38">
-        <v>9.411461157777865</v>
+        <v>9.416089333966491</v>
       </c>
       <c r="E38">
-        <v>-1.672800000000001</v>
+        <v>-1.5726</v>
       </c>
       <c r="F38">
-        <v>3.6072</v>
+        <v>3.7074</v>
       </c>
       <c r="G38">
         <v>1.28</v>
@@ -4397,28 +4397,28 @@
         <v>1.64</v>
       </c>
       <c r="M38">
-        <v>0.1929852</v>
+        <v>0.1983459</v>
       </c>
       <c r="N38">
-        <v>1.4470148</v>
+        <v>1.4416541</v>
       </c>
       <c r="O38">
-        <v>0.14470148</v>
+        <v>0.14416541</v>
       </c>
       <c r="P38">
-        <v>1.30231332</v>
+        <v>1.29748869</v>
       </c>
       <c r="Q38">
-        <v>2.67231332</v>
+        <v>2.66748869</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1643211695774486</v>
+        <v>0.1660775591681043</v>
       </c>
       <c r="T38">
-        <v>1.833484799114307</v>
+        <v>1.860655587482924</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.498060991205541</v>
+        <v>8.268383667118904</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1224443622759057</v>
+        <v>0.1223891760222443</v>
       </c>
       <c r="C39">
-        <v>6.988689333966491</v>
+        <v>6.893122064294615</v>
       </c>
       <c r="D39">
-        <v>9.416089333966491</v>
+        <v>9.420722064294615</v>
       </c>
       <c r="E39">
-        <v>-1.5726</v>
+        <v>-1.4724</v>
       </c>
       <c r="F39">
-        <v>3.7074</v>
+        <v>3.8076</v>
       </c>
       <c r="G39">
         <v>1.28</v>
@@ -4479,28 +4479,28 @@
         <v>1.64</v>
       </c>
       <c r="M39">
-        <v>0.1983459</v>
+        <v>0.2037066</v>
       </c>
       <c r="N39">
-        <v>1.4416541</v>
+        <v>1.4362934</v>
       </c>
       <c r="O39">
-        <v>0.14416541</v>
+        <v>0.14362934</v>
       </c>
       <c r="P39">
-        <v>1.29748869</v>
+        <v>1.29266406</v>
       </c>
       <c r="Q39">
-        <v>2.66748869</v>
+        <v>2.66266406</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1660775591681043</v>
+        <v>0.1678906064874909</v>
       </c>
       <c r="T39">
-        <v>1.860655587482924</v>
+        <v>1.888702852895691</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.268383667118904</v>
+        <v>8.050794623247356</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1223891760222443</v>
+        <v>0.122333989768583</v>
       </c>
       <c r="C40">
-        <v>6.893122064294615</v>
+        <v>6.797559355487481</v>
       </c>
       <c r="D40">
-        <v>9.420722064294615</v>
+        <v>9.425359355487481</v>
       </c>
       <c r="E40">
-        <v>-1.4724</v>
+        <v>-1.3722</v>
       </c>
       <c r="F40">
-        <v>3.8076</v>
+        <v>3.9078</v>
       </c>
       <c r="G40">
         <v>1.28</v>
@@ -4561,28 +4561,28 @@
         <v>1.64</v>
       </c>
       <c r="M40">
-        <v>0.2037066</v>
+        <v>0.2090673</v>
       </c>
       <c r="N40">
-        <v>1.4362934</v>
+        <v>1.4309327</v>
       </c>
       <c r="O40">
-        <v>0.14362934</v>
+        <v>0.14309327</v>
       </c>
       <c r="P40">
-        <v>1.29266406</v>
+        <v>1.28783943</v>
       </c>
       <c r="Q40">
-        <v>2.66266406</v>
+        <v>2.65783943</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1678906064874909</v>
+        <v>0.1697630979812836</v>
       </c>
       <c r="T40">
-        <v>1.888702852895691</v>
+        <v>1.917669700781007</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.050794623247356</v>
+        <v>7.844363991882038</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.122333989768583</v>
+        <v>0.1222788035149216</v>
       </c>
       <c r="C41">
-        <v>6.797559355487481</v>
+        <v>6.702001214283576</v>
       </c>
       <c r="D41">
-        <v>9.425359355487481</v>
+        <v>9.430001214283577</v>
       </c>
       <c r="E41">
-        <v>-1.3722</v>
+        <v>-1.272</v>
       </c>
       <c r="F41">
-        <v>3.9078</v>
+        <v>4.008</v>
       </c>
       <c r="G41">
         <v>1.28</v>
@@ -4643,28 +4643,28 @@
         <v>1.64</v>
       </c>
       <c r="M41">
-        <v>0.2090673</v>
+        <v>0.214428</v>
       </c>
       <c r="N41">
-        <v>1.4309327</v>
+        <v>1.425572</v>
       </c>
       <c r="O41">
-        <v>0.14309327</v>
+        <v>0.1425572</v>
       </c>
       <c r="P41">
-        <v>1.28783943</v>
+        <v>1.2830148</v>
       </c>
       <c r="Q41">
-        <v>2.65783943</v>
+        <v>2.6530148</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1697630979812836</v>
+        <v>0.1716980058582027</v>
       </c>
       <c r="T41">
-        <v>1.917669700781007</v>
+        <v>1.947602110262501</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.844363991882038</v>
+        <v>7.648254892084987</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1222788035149216</v>
+        <v>0.1225188172612602</v>
       </c>
       <c r="C42">
-        <v>6.702001214283576</v>
+        <v>6.581646263639611</v>
       </c>
       <c r="D42">
-        <v>9.430001214283577</v>
+        <v>9.409846263639611</v>
       </c>
       <c r="E42">
-        <v>-1.272</v>
+        <v>-1.1718</v>
       </c>
       <c r="F42">
-        <v>4.008</v>
+        <v>4.1082</v>
       </c>
       <c r="G42">
         <v>1.28</v>
@@ -4725,45 +4725,45 @@
         <v>1.64</v>
       </c>
       <c r="M42">
-        <v>0.214428</v>
+        <v>0.22307526</v>
       </c>
       <c r="N42">
-        <v>1.425572</v>
+        <v>1.41692474</v>
       </c>
       <c r="O42">
-        <v>0.1425572</v>
+        <v>0.141692474</v>
       </c>
       <c r="P42">
-        <v>1.2830148</v>
+        <v>1.275232266</v>
       </c>
       <c r="Q42">
-        <v>2.6530148</v>
+        <v>2.645232266</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1716980058582027</v>
+        <v>0.1736985038326444</v>
       </c>
       <c r="T42">
-        <v>1.947602110262501</v>
+        <v>1.978549177692519</v>
       </c>
       <c r="U42">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.1</v>
       </c>
       <c r="W42">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>7.648254892084987</v>
+        <v>7.351778946710629</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1225188172612602</v>
+        <v>0.1224708310075988</v>
       </c>
       <c r="C43">
-        <v>6.581646263639611</v>
+        <v>6.485468974975039</v>
       </c>
       <c r="D43">
-        <v>9.409846263639611</v>
+        <v>9.41386897497504</v>
       </c>
       <c r="E43">
-        <v>-1.1718</v>
+        <v>-1.0716</v>
       </c>
       <c r="F43">
-        <v>4.1082</v>
+        <v>4.2084</v>
       </c>
       <c r="G43">
         <v>1.28</v>
@@ -4807,28 +4807,28 @@
         <v>1.64</v>
       </c>
       <c r="M43">
-        <v>0.22307526</v>
+        <v>0.22851612</v>
       </c>
       <c r="N43">
-        <v>1.41692474</v>
+        <v>1.41148388</v>
       </c>
       <c r="O43">
-        <v>0.141692474</v>
+        <v>0.141148388</v>
       </c>
       <c r="P43">
-        <v>1.275232266</v>
+        <v>1.270335492</v>
       </c>
       <c r="Q43">
-        <v>2.645232266</v>
+        <v>2.640335492</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1736985038326444</v>
+        <v>0.1757679844958601</v>
       </c>
       <c r="T43">
-        <v>1.978549177692519</v>
+        <v>2.010563385378745</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.351778946710629</v>
+        <v>7.176736590836565</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1224708310075989</v>
+        <v>0.1224228447539375</v>
       </c>
       <c r="C44">
-        <v>6.485468974975038</v>
+        <v>6.389295127201401</v>
       </c>
       <c r="D44">
-        <v>9.413868974975038</v>
+        <v>9.417895127201401</v>
       </c>
       <c r="E44">
-        <v>-1.071600000000001</v>
+        <v>-0.9714000000000009</v>
       </c>
       <c r="F44">
-        <v>4.208399999999999</v>
+        <v>4.308599999999999</v>
       </c>
       <c r="G44">
         <v>1.28</v>
@@ -4889,28 +4889,28 @@
         <v>1.64</v>
       </c>
       <c r="M44">
-        <v>0.22851612</v>
+        <v>0.23395698</v>
       </c>
       <c r="N44">
-        <v>1.41148388</v>
+        <v>1.40604302</v>
       </c>
       <c r="O44">
-        <v>0.141148388</v>
+        <v>0.140604302</v>
       </c>
       <c r="P44">
-        <v>1.270335492</v>
+        <v>1.265438718</v>
       </c>
       <c r="Q44">
-        <v>2.640335492</v>
+        <v>2.635438718</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1757679844958601</v>
+        <v>0.1779100785156797</v>
       </c>
       <c r="T44">
-        <v>2.010563385378745</v>
+        <v>2.043700898597821</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.176736590836568</v>
+        <v>7.00983573988688</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1224228447539375</v>
+        <v>0.1223748585002761</v>
       </c>
       <c r="C45">
-        <v>6.389295127201401</v>
+        <v>6.293124724735415</v>
       </c>
       <c r="D45">
-        <v>9.417895127201401</v>
+        <v>9.421924724735415</v>
       </c>
       <c r="E45">
-        <v>-0.9714000000000009</v>
+        <v>-0.8712</v>
       </c>
       <c r="F45">
-        <v>4.308599999999999</v>
+        <v>4.4088</v>
       </c>
       <c r="G45">
         <v>1.28</v>
@@ -4971,28 +4971,28 @@
         <v>1.64</v>
       </c>
       <c r="M45">
-        <v>0.23395698</v>
+        <v>0.23939784</v>
       </c>
       <c r="N45">
-        <v>1.40604302</v>
+        <v>1.40060216</v>
       </c>
       <c r="O45">
-        <v>0.140604302</v>
+        <v>0.140060216</v>
       </c>
       <c r="P45">
-        <v>1.265438718</v>
+        <v>1.260541944</v>
       </c>
       <c r="Q45">
-        <v>2.635438718</v>
+        <v>2.630541944</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1779100785156797</v>
+        <v>0.1801286758933502</v>
       </c>
       <c r="T45">
-        <v>2.043700898597821</v>
+        <v>2.078021894431865</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.00983573988688</v>
+        <v>6.850521291253085</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1223748585002761</v>
+        <v>0.1223268722466147</v>
       </c>
       <c r="C46">
-        <v>6.293124724735415</v>
+        <v>6.196957772001369</v>
       </c>
       <c r="D46">
-        <v>9.421924724735415</v>
+        <v>9.42595777200137</v>
       </c>
       <c r="E46">
-        <v>-0.8712</v>
+        <v>-0.7709999999999999</v>
       </c>
       <c r="F46">
-        <v>4.4088</v>
+        <v>4.509</v>
       </c>
       <c r="G46">
         <v>1.28</v>
@@ -5053,28 +5053,28 @@
         <v>1.64</v>
       </c>
       <c r="M46">
-        <v>0.23939784</v>
+        <v>0.2448387</v>
       </c>
       <c r="N46">
-        <v>1.40060216</v>
+        <v>1.3951613</v>
       </c>
       <c r="O46">
-        <v>0.140060216</v>
+        <v>0.13951613</v>
       </c>
       <c r="P46">
-        <v>1.260541944</v>
+        <v>1.25564517</v>
       </c>
       <c r="Q46">
-        <v>2.630541944</v>
+        <v>2.62564517</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1801286758933502</v>
+        <v>0.1824279495392995</v>
       </c>
       <c r="T46">
-        <v>2.078021894431865</v>
+        <v>2.113590926478055</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.850521291253085</v>
+        <v>6.698287484780795</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1223268722466147</v>
+        <v>0.1222788859929533</v>
       </c>
       <c r="C47">
-        <v>6.196957772001369</v>
+        <v>6.100794273431121</v>
       </c>
       <c r="D47">
-        <v>9.42595777200137</v>
+        <v>9.429994273431122</v>
       </c>
       <c r="E47">
-        <v>-0.7709999999999999</v>
+        <v>-0.6707999999999998</v>
       </c>
       <c r="F47">
-        <v>4.509</v>
+        <v>4.6092</v>
       </c>
       <c r="G47">
         <v>1.28</v>
@@ -5135,28 +5135,28 @@
         <v>1.64</v>
       </c>
       <c r="M47">
-        <v>0.2448387</v>
+        <v>0.25027956</v>
       </c>
       <c r="N47">
-        <v>1.3951613</v>
+        <v>1.38972044</v>
       </c>
       <c r="O47">
-        <v>0.13951613</v>
+        <v>0.138972044</v>
       </c>
       <c r="P47">
-        <v>1.25564517</v>
+        <v>1.250748396</v>
       </c>
       <c r="Q47">
-        <v>2.62564517</v>
+        <v>2.620748396</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1824279495392995</v>
+        <v>0.1848123814684321</v>
       </c>
       <c r="T47">
-        <v>2.113590926478055</v>
+        <v>2.150477330081511</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.698287484780795</v>
+        <v>6.552672539459473</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1222788859929533</v>
+        <v>0.122230899739292</v>
       </c>
       <c r="C48">
-        <v>6.100794273431121</v>
+        <v>6.004634233464129</v>
       </c>
       <c r="D48">
-        <v>9.429994273431122</v>
+        <v>9.43403423346413</v>
       </c>
       <c r="E48">
-        <v>-0.6707999999999998</v>
+        <v>-0.5705999999999998</v>
       </c>
       <c r="F48">
-        <v>4.6092</v>
+        <v>4.7094</v>
       </c>
       <c r="G48">
         <v>1.28</v>
@@ -5217,28 +5217,28 @@
         <v>1.64</v>
       </c>
       <c r="M48">
-        <v>0.25027956</v>
+        <v>0.25572042</v>
       </c>
       <c r="N48">
-        <v>1.38972044</v>
+        <v>1.38427958</v>
       </c>
       <c r="O48">
-        <v>0.138972044</v>
+        <v>0.138427958</v>
       </c>
       <c r="P48">
-        <v>1.250748396</v>
+        <v>1.245851622</v>
       </c>
       <c r="Q48">
-        <v>2.620748396</v>
+        <v>2.615851622</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1848123814684321</v>
+        <v>0.1872867919609282</v>
       </c>
       <c r="T48">
-        <v>2.150477330081511</v>
+        <v>2.188755673443588</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.552672539459473</v>
+        <v>6.413253974790122</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.122230899739292</v>
+        <v>0.1221829134856306</v>
       </c>
       <c r="C49">
-        <v>6.004634233464129</v>
+        <v>5.90847765654746</v>
       </c>
       <c r="D49">
-        <v>9.43403423346413</v>
+        <v>9.438077656547462</v>
       </c>
       <c r="E49">
-        <v>-0.5705999999999998</v>
+        <v>-0.4703999999999997</v>
       </c>
       <c r="F49">
-        <v>4.7094</v>
+        <v>4.809600000000001</v>
       </c>
       <c r="G49">
         <v>1.28</v>
@@ -5299,28 +5299,28 @@
         <v>1.64</v>
       </c>
       <c r="M49">
-        <v>0.25572042</v>
+        <v>0.2611612800000001</v>
       </c>
       <c r="N49">
-        <v>1.38427958</v>
+        <v>1.37883872</v>
       </c>
       <c r="O49">
-        <v>0.138427958</v>
+        <v>0.137883872</v>
       </c>
       <c r="P49">
-        <v>1.245851622</v>
+        <v>1.240954848</v>
       </c>
       <c r="Q49">
-        <v>2.615851622</v>
+        <v>2.610954848</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1872867919609282</v>
+        <v>0.1898563720877511</v>
       </c>
       <c r="T49">
-        <v>2.188755673443588</v>
+        <v>2.22850626078113</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.413253974790122</v>
+        <v>6.279644516981994</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1221829134856306</v>
+        <v>0.1221349272319692</v>
       </c>
       <c r="C50">
-        <v>5.908477656547461</v>
+        <v>5.812324547135815</v>
       </c>
       <c r="D50">
-        <v>9.438077656547462</v>
+        <v>9.442124547135816</v>
       </c>
       <c r="E50">
-        <v>-0.4704000000000006</v>
+        <v>-0.3702000000000005</v>
       </c>
       <c r="F50">
-        <v>4.8096</v>
+        <v>4.9098</v>
       </c>
       <c r="G50">
         <v>1.28</v>
@@ -5381,28 +5381,28 @@
         <v>1.64</v>
       </c>
       <c r="M50">
-        <v>0.26116128</v>
+        <v>0.26660214</v>
       </c>
       <c r="N50">
-        <v>1.37883872</v>
+        <v>1.37339786</v>
       </c>
       <c r="O50">
-        <v>0.137883872</v>
+        <v>0.137339786</v>
       </c>
       <c r="P50">
-        <v>1.240954848</v>
+        <v>1.236058074</v>
       </c>
       <c r="Q50">
-        <v>2.610954848</v>
+        <v>2.606058074</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1898563720877511</v>
+        <v>0.1925267200626847</v>
       </c>
       <c r="T50">
-        <v>2.22850626078113</v>
+        <v>2.269815694680929</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.279644516981995</v>
+        <v>6.151488506431343</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1221349272319692</v>
+        <v>0.1225369409783078</v>
       </c>
       <c r="C51">
-        <v>5.812324547135815</v>
+        <v>5.678327837785211</v>
       </c>
       <c r="D51">
-        <v>9.442124547135816</v>
+        <v>9.408327837785212</v>
       </c>
       <c r="E51">
-        <v>-0.3702000000000005</v>
+        <v>-0.2700000000000005</v>
       </c>
       <c r="F51">
-        <v>4.9098</v>
+        <v>5.01</v>
       </c>
       <c r="G51">
         <v>1.28</v>
@@ -5463,45 +5463,45 @@
         <v>1.64</v>
       </c>
       <c r="M51">
-        <v>0.26660214</v>
+        <v>0.277053</v>
       </c>
       <c r="N51">
-        <v>1.37339786</v>
+        <v>1.362947</v>
       </c>
       <c r="O51">
-        <v>0.137339786</v>
+        <v>0.1362947</v>
       </c>
       <c r="P51">
-        <v>1.236058074</v>
+        <v>1.2266523</v>
       </c>
       <c r="Q51">
-        <v>2.606058074</v>
+        <v>2.5966523</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1925267200626847</v>
+        <v>0.1953038819566157</v>
       </c>
       <c r="T51">
-        <v>2.269815694680929</v>
+        <v>2.312777505936719</v>
       </c>
       <c r="U51">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.1</v>
       </c>
       <c r="W51">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>6.151488506431343</v>
+        <v>5.919445015935578</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1225369409783078</v>
+        <v>0.1224979547246464</v>
       </c>
       <c r="C52">
-        <v>5.678327837785211</v>
+        <v>5.58139475787783</v>
       </c>
       <c r="D52">
-        <v>9.408327837785212</v>
+        <v>9.411594757877831</v>
       </c>
       <c r="E52">
-        <v>-0.2700000000000005</v>
+        <v>-0.1698000000000004</v>
       </c>
       <c r="F52">
-        <v>5.01</v>
+        <v>5.1102</v>
       </c>
       <c r="G52">
         <v>1.28</v>
@@ -5545,28 +5545,28 @@
         <v>1.64</v>
       </c>
       <c r="M52">
-        <v>0.277053</v>
+        <v>0.28259406</v>
       </c>
       <c r="N52">
-        <v>1.362947</v>
+        <v>1.35740594</v>
       </c>
       <c r="O52">
-        <v>0.1362947</v>
+        <v>0.135740594</v>
       </c>
       <c r="P52">
-        <v>1.2266523</v>
+        <v>1.221665346</v>
       </c>
       <c r="Q52">
-        <v>2.5966523</v>
+        <v>2.591665346</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1953038819566157</v>
+        <v>0.1981943973972377</v>
       </c>
       <c r="T52">
-        <v>2.312777505936719</v>
+        <v>2.357492860509073</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.919445015935578</v>
+        <v>5.803377466603508</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1224979547246464</v>
+        <v>0.1224589684709851</v>
       </c>
       <c r="C53">
-        <v>5.58139475787783</v>
+        <v>5.484463947549983</v>
       </c>
       <c r="D53">
-        <v>9.411594757877831</v>
+        <v>9.414863947549984</v>
       </c>
       <c r="E53">
-        <v>-0.1698000000000004</v>
+        <v>-0.06960000000000033</v>
       </c>
       <c r="F53">
-        <v>5.1102</v>
+        <v>5.2104</v>
       </c>
       <c r="G53">
         <v>1.28</v>
@@ -5627,28 +5627,28 @@
         <v>1.64</v>
       </c>
       <c r="M53">
-        <v>0.28259406</v>
+        <v>0.28813512</v>
       </c>
       <c r="N53">
-        <v>1.35740594</v>
+        <v>1.35186488</v>
       </c>
       <c r="O53">
-        <v>0.135740594</v>
+        <v>0.135186488</v>
       </c>
       <c r="P53">
-        <v>1.221665346</v>
+        <v>1.216678392</v>
       </c>
       <c r="Q53">
-        <v>2.591665346</v>
+        <v>2.586678392</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1981943973972377</v>
+        <v>0.2012053509812189</v>
       </c>
       <c r="T53">
-        <v>2.357492860509073</v>
+        <v>2.404071354855274</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.803377466603508</v>
+        <v>5.69177405378421</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1224589684709851</v>
+        <v>0.1224199822173237</v>
       </c>
       <c r="C54">
-        <v>5.484463947549983</v>
+        <v>5.387535409167564</v>
       </c>
       <c r="D54">
-        <v>9.414863947549984</v>
+        <v>9.418135409167565</v>
       </c>
       <c r="E54">
-        <v>-0.06960000000000033</v>
+        <v>0.03059999999999974</v>
       </c>
       <c r="F54">
-        <v>5.2104</v>
+        <v>5.3106</v>
       </c>
       <c r="G54">
         <v>1.28</v>
@@ -5709,28 +5709,28 @@
         <v>1.64</v>
       </c>
       <c r="M54">
-        <v>0.28813512</v>
+        <v>0.29367618</v>
       </c>
       <c r="N54">
-        <v>1.35186488</v>
+        <v>1.34632382</v>
       </c>
       <c r="O54">
-        <v>0.135186488</v>
+        <v>0.134632382</v>
       </c>
       <c r="P54">
-        <v>1.216678392</v>
+        <v>1.211691438</v>
       </c>
       <c r="Q54">
-        <v>2.586678392</v>
+        <v>2.581691438</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2012053509812189</v>
+        <v>0.2043444302496249</v>
       </c>
       <c r="T54">
-        <v>2.404071354855274</v>
+        <v>2.452631912790675</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.69177405378421</v>
+        <v>5.584382090505262</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1224199822173237</v>
+        <v>0.1223809959636623</v>
       </c>
       <c r="C55">
-        <v>5.387535409167564</v>
+        <v>5.29060914509974</v>
       </c>
       <c r="D55">
-        <v>9.418135409167565</v>
+        <v>9.421409145099741</v>
       </c>
       <c r="E55">
-        <v>0.03059999999999974</v>
+        <v>0.1307999999999998</v>
       </c>
       <c r="F55">
-        <v>5.3106</v>
+        <v>5.4108</v>
       </c>
       <c r="G55">
         <v>1.28</v>
@@ -5791,28 +5791,28 @@
         <v>1.64</v>
       </c>
       <c r="M55">
-        <v>0.29367618</v>
+        <v>0.29921724</v>
       </c>
       <c r="N55">
-        <v>1.34632382</v>
+        <v>1.34078276</v>
       </c>
       <c r="O55">
-        <v>0.134632382</v>
+        <v>0.134078276</v>
       </c>
       <c r="P55">
-        <v>1.211691438</v>
+        <v>1.206704484</v>
       </c>
       <c r="Q55">
-        <v>2.581691438</v>
+        <v>2.576704484</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2043444302496249</v>
+        <v>0.2076199912253529</v>
       </c>
       <c r="T55">
-        <v>2.452631912790675</v>
+        <v>2.503303799331964</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.584382090505262</v>
+        <v>5.480967607347758</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1223809959636623</v>
+        <v>0.1223420097100009</v>
       </c>
       <c r="C56">
-        <v>5.29060914509974</v>
+        <v>5.193685157719</v>
       </c>
       <c r="D56">
-        <v>9.421409145099741</v>
+        <v>9.424685157719001</v>
       </c>
       <c r="E56">
-        <v>0.1307999999999998</v>
+        <v>0.2309999999999999</v>
       </c>
       <c r="F56">
-        <v>5.4108</v>
+        <v>5.511</v>
       </c>
       <c r="G56">
         <v>1.28</v>
@@ -5873,28 +5873,28 @@
         <v>1.64</v>
       </c>
       <c r="M56">
-        <v>0.29921724</v>
+        <v>0.3047583</v>
       </c>
       <c r="N56">
-        <v>1.34078276</v>
+        <v>1.3352417</v>
       </c>
       <c r="O56">
-        <v>0.134078276</v>
+        <v>0.13352417</v>
       </c>
       <c r="P56">
-        <v>1.206704484</v>
+        <v>1.20171753</v>
       </c>
       <c r="Q56">
-        <v>2.576704484</v>
+        <v>2.57171753</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2076199912253529</v>
+        <v>0.211041132688891</v>
       </c>
       <c r="T56">
-        <v>2.503303799331964</v>
+        <v>2.556227769719532</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.480967607347758</v>
+        <v>5.381313650850525</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1223420097100009</v>
+        <v>0.1223030234563396</v>
       </c>
       <c r="C57">
-        <v>5.193685157719</v>
+        <v>5.096763449401113</v>
       </c>
       <c r="D57">
-        <v>9.424685157719001</v>
+        <v>9.427963449401114</v>
       </c>
       <c r="E57">
-        <v>0.2309999999999999</v>
+        <v>0.3311999999999999</v>
       </c>
       <c r="F57">
-        <v>5.511</v>
+        <v>5.6112</v>
       </c>
       <c r="G57">
         <v>1.28</v>
@@ -5955,28 +5955,28 @@
         <v>1.64</v>
       </c>
       <c r="M57">
-        <v>0.3047583</v>
+        <v>0.31029936</v>
       </c>
       <c r="N57">
-        <v>1.3352417</v>
+        <v>1.32970064</v>
       </c>
       <c r="O57">
-        <v>0.13352417</v>
+        <v>0.132970064</v>
       </c>
       <c r="P57">
-        <v>1.20171753</v>
+        <v>1.196730576</v>
       </c>
       <c r="Q57">
-        <v>2.57171753</v>
+        <v>2.566730575999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.211041132688891</v>
+        <v>0.2146177805825899</v>
       </c>
       <c r="T57">
-        <v>2.556227769719532</v>
+        <v>2.611557375124717</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.381313650850525</v>
+        <v>5.285218764228194</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1223030234563396</v>
+        <v>0.1222640372026782</v>
       </c>
       <c r="C58">
-        <v>5.096763449401113</v>
+        <v>4.999844022525157</v>
       </c>
       <c r="D58">
-        <v>9.427963449401114</v>
+        <v>9.431244022525158</v>
       </c>
       <c r="E58">
-        <v>0.3311999999999999</v>
+        <v>0.4314</v>
       </c>
       <c r="F58">
-        <v>5.6112</v>
+        <v>5.7114</v>
       </c>
       <c r="G58">
         <v>1.28</v>
@@ -6037,28 +6037,28 @@
         <v>1.64</v>
       </c>
       <c r="M58">
-        <v>0.31029936</v>
+        <v>0.31584042</v>
       </c>
       <c r="N58">
-        <v>1.32970064</v>
+        <v>1.32415958</v>
       </c>
       <c r="O58">
-        <v>0.132970064</v>
+        <v>0.132415958</v>
       </c>
       <c r="P58">
-        <v>1.196730576</v>
+        <v>1.191743622</v>
       </c>
       <c r="Q58">
-        <v>2.566730575999999</v>
+        <v>2.561743622</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2146177805825899</v>
+        <v>0.2183607841922749</v>
       </c>
       <c r="T58">
-        <v>2.611557375124717</v>
+        <v>2.669460450548747</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.285218764228194</v>
+        <v>5.192495628013664</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1222640372026782</v>
+        <v>0.1222250509490168</v>
       </c>
       <c r="C59">
-        <v>4.999844022525157</v>
+        <v>4.902926879473529</v>
       </c>
       <c r="D59">
-        <v>9.431244022525158</v>
+        <v>9.43452687947353</v>
       </c>
       <c r="E59">
-        <v>0.4314</v>
+        <v>0.5316000000000001</v>
       </c>
       <c r="F59">
-        <v>5.7114</v>
+        <v>5.8116</v>
       </c>
       <c r="G59">
         <v>1.28</v>
@@ -6119,28 +6119,28 @@
         <v>1.64</v>
       </c>
       <c r="M59">
-        <v>0.31584042</v>
+        <v>0.3213814800000001</v>
       </c>
       <c r="N59">
-        <v>1.32415958</v>
+        <v>1.31861852</v>
       </c>
       <c r="O59">
-        <v>0.132415958</v>
+        <v>0.131861852</v>
       </c>
       <c r="P59">
-        <v>1.191743622</v>
+        <v>1.186756668</v>
       </c>
       <c r="Q59">
-        <v>2.561743622</v>
+        <v>2.556756668</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2183607841922749</v>
+        <v>0.2222820260690877</v>
       </c>
       <c r="T59">
-        <v>2.669460450548747</v>
+        <v>2.730120815278684</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.192495628013664</v>
+        <v>5.102969841323773</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1222250509490168</v>
+        <v>0.1221860646953554</v>
       </c>
       <c r="C60">
-        <v>4.902926879473532</v>
+        <v>4.806012022631947</v>
       </c>
       <c r="D60">
-        <v>9.434526879473532</v>
+        <v>9.437812022631947</v>
       </c>
       <c r="E60">
-        <v>0.5315999999999992</v>
+        <v>0.6317999999999993</v>
       </c>
       <c r="F60">
-        <v>5.811599999999999</v>
+        <v>5.911799999999999</v>
       </c>
       <c r="G60">
         <v>1.28</v>
@@ -6201,28 +6201,28 @@
         <v>1.64</v>
       </c>
       <c r="M60">
-        <v>0.32138148</v>
+        <v>0.32692254</v>
       </c>
       <c r="N60">
-        <v>1.31861852</v>
+        <v>1.31307746</v>
       </c>
       <c r="O60">
-        <v>0.131861852</v>
+        <v>0.131307746</v>
       </c>
       <c r="P60">
-        <v>1.186756668</v>
+        <v>1.181769714</v>
       </c>
       <c r="Q60">
-        <v>2.556756668</v>
+        <v>2.551769714</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2222820260690876</v>
+        <v>0.2263945480374523</v>
       </c>
       <c r="T60">
-        <v>2.730120815278684</v>
+        <v>2.793740222190568</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.102969841323774</v>
+        <v>5.016478827064049</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1221860646953554</v>
+        <v>0.122147078441694</v>
       </c>
       <c r="C61">
-        <v>4.806012022631947</v>
+        <v>4.709099454389443</v>
       </c>
       <c r="D61">
-        <v>9.437812022631947</v>
+        <v>9.441099454389443</v>
       </c>
       <c r="E61">
-        <v>0.6317999999999993</v>
+        <v>0.7319999999999993</v>
       </c>
       <c r="F61">
-        <v>5.911799999999999</v>
+        <v>6.012</v>
       </c>
       <c r="G61">
         <v>1.28</v>
@@ -6283,28 +6283,28 @@
         <v>1.64</v>
       </c>
       <c r="M61">
-        <v>0.32692254</v>
+        <v>0.3324636</v>
       </c>
       <c r="N61">
-        <v>1.31307746</v>
+        <v>1.3075364</v>
       </c>
       <c r="O61">
-        <v>0.131307746</v>
+        <v>0.13075364</v>
       </c>
       <c r="P61">
-        <v>1.181769714</v>
+        <v>1.17678276</v>
       </c>
       <c r="Q61">
-        <v>2.551769714</v>
+        <v>2.54678276</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2263945480374523</v>
+        <v>0.2307126961042351</v>
       </c>
       <c r="T61">
-        <v>2.793740222190568</v>
+        <v>2.860540599448047</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.016478827064049</v>
+        <v>4.932870846612982</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.122147078441694</v>
+        <v>0.1221080921880327</v>
       </c>
       <c r="C62">
-        <v>4.709099454389443</v>
+        <v>4.612189177138379</v>
       </c>
       <c r="D62">
-        <v>9.441099454389443</v>
+        <v>9.44438917713838</v>
       </c>
       <c r="E62">
-        <v>0.7319999999999993</v>
+        <v>0.8321999999999994</v>
       </c>
       <c r="F62">
-        <v>6.012</v>
+        <v>6.1122</v>
       </c>
       <c r="G62">
         <v>1.28</v>
@@ -6365,28 +6365,28 @@
         <v>1.64</v>
       </c>
       <c r="M62">
-        <v>0.3324636</v>
+        <v>0.33800466</v>
       </c>
       <c r="N62">
-        <v>1.3075364</v>
+        <v>1.30199534</v>
       </c>
       <c r="O62">
-        <v>0.13075364</v>
+        <v>0.130199534</v>
       </c>
       <c r="P62">
-        <v>1.17678276</v>
+        <v>1.171795806</v>
       </c>
       <c r="Q62">
-        <v>2.54678276</v>
+        <v>2.541795806</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2307126961042351</v>
+        <v>0.2352522876616223</v>
       </c>
       <c r="T62">
-        <v>2.860540599448047</v>
+        <v>2.930766637077705</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.932870846612982</v>
+        <v>4.852004111422605</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1221080921880327</v>
+        <v>0.1220691059343713</v>
       </c>
       <c r="C63">
-        <v>4.612189177138379</v>
+        <v>4.515281193274464</v>
       </c>
       <c r="D63">
-        <v>9.44438917713838</v>
+        <v>9.447681193274464</v>
       </c>
       <c r="E63">
-        <v>0.8321999999999994</v>
+        <v>0.9323999999999995</v>
       </c>
       <c r="F63">
-        <v>6.1122</v>
+        <v>6.2124</v>
       </c>
       <c r="G63">
         <v>1.28</v>
@@ -6447,28 +6447,28 @@
         <v>1.64</v>
       </c>
       <c r="M63">
-        <v>0.33800466</v>
+        <v>0.34354572</v>
       </c>
       <c r="N63">
-        <v>1.30199534</v>
+        <v>1.29645428</v>
       </c>
       <c r="O63">
-        <v>0.130199534</v>
+        <v>0.129645428</v>
       </c>
       <c r="P63">
-        <v>1.171795806</v>
+        <v>1.166808852</v>
       </c>
       <c r="Q63">
-        <v>2.541795806</v>
+        <v>2.536808852</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2352522876616223</v>
+        <v>0.2400308050904508</v>
       </c>
       <c r="T63">
-        <v>2.930766637077705</v>
+        <v>3.004688781951029</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.852004111422605</v>
+        <v>4.773745980593208</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1220691059343713</v>
+        <v>0.1220301196807099</v>
       </c>
       <c r="C64">
-        <v>4.515281193274464</v>
+        <v>4.418375505196739</v>
       </c>
       <c r="D64">
-        <v>9.447681193274464</v>
+        <v>9.450975505196739</v>
       </c>
       <c r="E64">
-        <v>0.9323999999999995</v>
+        <v>1.0326</v>
       </c>
       <c r="F64">
-        <v>6.2124</v>
+        <v>6.3126</v>
       </c>
       <c r="G64">
         <v>1.28</v>
@@ -6529,28 +6529,28 @@
         <v>1.64</v>
       </c>
       <c r="M64">
-        <v>0.34354572</v>
+        <v>0.34908678</v>
       </c>
       <c r="N64">
-        <v>1.29645428</v>
+        <v>1.29091322</v>
       </c>
       <c r="O64">
-        <v>0.129645428</v>
+        <v>0.129091322</v>
       </c>
       <c r="P64">
-        <v>1.166808852</v>
+        <v>1.161821898</v>
       </c>
       <c r="Q64">
-        <v>2.536808852</v>
+        <v>2.531821898</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2400308050904508</v>
+        <v>0.2450676207586755</v>
       </c>
       <c r="T64">
-        <v>3.004688781951029</v>
+        <v>3.082606718439126</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.773745980593208</v>
+        <v>4.697972234869507</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1220301196807099</v>
+        <v>0.1219911334270486</v>
       </c>
       <c r="C65">
-        <v>4.418375505196739</v>
+        <v>4.321472115307594</v>
       </c>
       <c r="D65">
-        <v>9.450975505196739</v>
+        <v>9.454272115307594</v>
       </c>
       <c r="E65">
-        <v>1.0326</v>
+        <v>1.1328</v>
       </c>
       <c r="F65">
-        <v>6.3126</v>
+        <v>6.4128</v>
       </c>
       <c r="G65">
         <v>1.28</v>
@@ -6611,28 +6611,28 @@
         <v>1.64</v>
       </c>
       <c r="M65">
-        <v>0.34908678</v>
+        <v>0.35462784</v>
       </c>
       <c r="N65">
-        <v>1.29091322</v>
+        <v>1.28537216</v>
       </c>
       <c r="O65">
-        <v>0.129091322</v>
+        <v>0.128537216</v>
       </c>
       <c r="P65">
-        <v>1.161821898</v>
+        <v>1.156834944</v>
       </c>
       <c r="Q65">
-        <v>2.531821898</v>
+        <v>2.526834944</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2450676207586755</v>
+        <v>0.2503842595195793</v>
       </c>
       <c r="T65">
-        <v>3.082606718439126</v>
+        <v>3.164853429176564</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.697972234869507</v>
+        <v>4.62456641869967</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1219911334270486</v>
+        <v>0.1219521471733872</v>
       </c>
       <c r="C66">
-        <v>4.321472115307594</v>
+        <v>4.224571026012775</v>
       </c>
       <c r="D66">
-        <v>9.454272115307594</v>
+        <v>9.457571026012776</v>
       </c>
       <c r="E66">
-        <v>1.1328</v>
+        <v>1.233</v>
       </c>
       <c r="F66">
-        <v>6.4128</v>
+        <v>6.513</v>
       </c>
       <c r="G66">
         <v>1.28</v>
@@ -6693,28 +6693,28 @@
         <v>1.64</v>
       </c>
       <c r="M66">
-        <v>0.35462784</v>
+        <v>0.3601689</v>
       </c>
       <c r="N66">
-        <v>1.28537216</v>
+        <v>1.2798311</v>
       </c>
       <c r="O66">
-        <v>0.128537216</v>
+        <v>0.12798311</v>
       </c>
       <c r="P66">
-        <v>1.156834944</v>
+        <v>1.15184799</v>
       </c>
       <c r="Q66">
-        <v>2.526834944</v>
+        <v>2.521847989999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2503842595195793</v>
+        <v>0.2560047062096776</v>
       </c>
       <c r="T66">
-        <v>3.164853429176564</v>
+        <v>3.251799951956139</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.62456641869967</v>
+        <v>4.553419243027367</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1219521471733872</v>
+        <v>0.1233981609197258</v>
       </c>
       <c r="C67">
-        <v>4.224571026012775</v>
+        <v>4.003534456656145</v>
       </c>
       <c r="D67">
-        <v>9.457571026012776</v>
+        <v>9.336734456656146</v>
       </c>
       <c r="E67">
-        <v>1.233</v>
+        <v>1.3332</v>
       </c>
       <c r="F67">
-        <v>6.513</v>
+        <v>6.6132</v>
       </c>
       <c r="G67">
         <v>1.28</v>
@@ -6775,45 +6775,45 @@
         <v>1.64</v>
       </c>
       <c r="M67">
-        <v>0.3601689</v>
+        <v>0.38224296</v>
       </c>
       <c r="N67">
-        <v>1.2798311</v>
+        <v>1.25775704</v>
       </c>
       <c r="O67">
-        <v>0.12798311</v>
+        <v>0.125775704</v>
       </c>
       <c r="P67">
-        <v>1.15184799</v>
+        <v>1.131981336</v>
       </c>
       <c r="Q67">
-        <v>2.521847989999999</v>
+        <v>2.501981336</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2560047062096776</v>
+        <v>0.2619557674109582</v>
       </c>
       <c r="T67">
-        <v>3.251799951956139</v>
+        <v>3.34386097607569</v>
       </c>
       <c r="U67">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V67">
         <v>0.1</v>
       </c>
       <c r="W67">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>4.553419243027367</v>
+        <v>4.290464891753663</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1233981609197258</v>
+        <v>0.1233816746660644</v>
       </c>
       <c r="C68">
-        <v>4.003534456656145</v>
+        <v>3.904694731313032</v>
       </c>
       <c r="D68">
-        <v>9.336734456656146</v>
+        <v>9.338094731313033</v>
       </c>
       <c r="E68">
-        <v>1.3332</v>
+        <v>1.4334</v>
       </c>
       <c r="F68">
-        <v>6.6132</v>
+        <v>6.7134</v>
       </c>
       <c r="G68">
         <v>1.28</v>
@@ -6857,28 +6857,28 @@
         <v>1.64</v>
       </c>
       <c r="M68">
-        <v>0.38224296</v>
+        <v>0.38803452</v>
       </c>
       <c r="N68">
-        <v>1.25775704</v>
+        <v>1.25196548</v>
       </c>
       <c r="O68">
-        <v>0.125775704</v>
+        <v>0.125196548</v>
       </c>
       <c r="P68">
-        <v>1.131981336</v>
+        <v>1.126768932</v>
       </c>
       <c r="Q68">
-        <v>2.501981336</v>
+        <v>2.496768932</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2619557674109582</v>
+        <v>0.268267498988074</v>
       </c>
       <c r="T68">
-        <v>3.34386097607569</v>
+        <v>3.441501456202487</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.290464891753663</v>
+        <v>4.226428102324503</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1233816746660644</v>
+        <v>0.1233651884124031</v>
       </c>
       <c r="C69">
-        <v>3.904694731313032</v>
+        <v>3.805855402386203</v>
       </c>
       <c r="D69">
-        <v>9.338094731313033</v>
+        <v>9.339455402386204</v>
       </c>
       <c r="E69">
-        <v>1.4334</v>
+        <v>1.5336</v>
       </c>
       <c r="F69">
-        <v>6.7134</v>
+        <v>6.8136</v>
       </c>
       <c r="G69">
         <v>1.28</v>
@@ -6939,28 +6939,28 @@
         <v>1.64</v>
       </c>
       <c r="M69">
-        <v>0.38803452</v>
+        <v>0.39382608</v>
       </c>
       <c r="N69">
-        <v>1.25196548</v>
+        <v>1.24617392</v>
       </c>
       <c r="O69">
-        <v>0.125196548</v>
+        <v>0.124617392</v>
       </c>
       <c r="P69">
-        <v>1.126768932</v>
+        <v>1.121556528</v>
       </c>
       <c r="Q69">
-        <v>2.496768932</v>
+        <v>2.491556528</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.268267498988074</v>
+        <v>0.2749737137887596</v>
       </c>
       <c r="T69">
-        <v>3.441501456202487</v>
+        <v>3.545244466337209</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.226428102324503</v>
+        <v>4.164274747878554</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1233651884124031</v>
+        <v>0.1233487021587417</v>
       </c>
       <c r="C70">
-        <v>3.805855402386203</v>
+        <v>3.707016470048965</v>
       </c>
       <c r="D70">
-        <v>9.339455402386204</v>
+        <v>9.340816470048965</v>
       </c>
       <c r="E70">
-        <v>1.5336</v>
+        <v>1.6338</v>
       </c>
       <c r="F70">
-        <v>6.8136</v>
+        <v>6.9138</v>
       </c>
       <c r="G70">
         <v>1.28</v>
@@ -7021,28 +7021,28 @@
         <v>1.64</v>
       </c>
       <c r="M70">
-        <v>0.39382608</v>
+        <v>0.3996176400000001</v>
       </c>
       <c r="N70">
-        <v>1.24617392</v>
+        <v>1.24038236</v>
       </c>
       <c r="O70">
-        <v>0.124617392</v>
+        <v>0.124038236</v>
       </c>
       <c r="P70">
-        <v>1.121556528</v>
+        <v>1.116344124</v>
       </c>
       <c r="Q70">
-        <v>2.491556528</v>
+        <v>2.486344124</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2749737137887596</v>
+        <v>0.2821125876088441</v>
       </c>
       <c r="T70">
-        <v>3.545244466337209</v>
+        <v>3.655680573899976</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.164274747878554</v>
+        <v>4.103922939938286</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1233487021587417</v>
+        <v>0.1233322159050803</v>
       </c>
       <c r="C71">
-        <v>3.707016470048965</v>
+        <v>3.608177934474731</v>
       </c>
       <c r="D71">
-        <v>9.340816470048965</v>
+        <v>9.342177934474732</v>
       </c>
       <c r="E71">
-        <v>1.6338</v>
+        <v>1.734</v>
       </c>
       <c r="F71">
-        <v>6.9138</v>
+        <v>7.014</v>
       </c>
       <c r="G71">
         <v>1.28</v>
@@ -7103,28 +7103,28 @@
         <v>1.64</v>
       </c>
       <c r="M71">
-        <v>0.3996176400000001</v>
+        <v>0.4054092</v>
       </c>
       <c r="N71">
-        <v>1.24038236</v>
+        <v>1.2345908</v>
       </c>
       <c r="O71">
-        <v>0.124038236</v>
+        <v>0.12345908</v>
       </c>
       <c r="P71">
-        <v>1.116344124</v>
+        <v>1.11113172</v>
       </c>
       <c r="Q71">
-        <v>2.486344124</v>
+        <v>2.48113172</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2821125876088441</v>
+        <v>0.2897273863502677</v>
       </c>
       <c r="T71">
-        <v>3.655680573899976</v>
+        <v>3.773479088633595</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.103922939938286</v>
+        <v>4.045295469367739</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1233322159050803</v>
+        <v>0.1255522296514189</v>
       </c>
       <c r="C72">
-        <v>3.608177934474731</v>
+        <v>3.328148023681148</v>
       </c>
       <c r="D72">
-        <v>9.342177934474732</v>
+        <v>9.162348023681149</v>
       </c>
       <c r="E72">
-        <v>1.734</v>
+        <v>1.8342</v>
       </c>
       <c r="F72">
-        <v>7.014</v>
+        <v>7.1142</v>
       </c>
       <c r="G72">
         <v>1.28</v>
@@ -7185,45 +7185,45 @@
         <v>1.64</v>
       </c>
       <c r="M72">
-        <v>0.4054092</v>
+        <v>0.43610046</v>
       </c>
       <c r="N72">
-        <v>1.2345908</v>
+        <v>1.20389954</v>
       </c>
       <c r="O72">
-        <v>0.12345908</v>
+        <v>0.120389954</v>
       </c>
       <c r="P72">
-        <v>1.11113172</v>
+        <v>1.083509586</v>
       </c>
       <c r="Q72">
-        <v>2.48113172</v>
+        <v>2.453509586</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2897273863502677</v>
+        <v>0.2978673436255825</v>
       </c>
       <c r="T72">
-        <v>3.773479088633595</v>
+        <v>3.899401638866085</v>
       </c>
       <c r="U72">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V72">
         <v>0.1</v>
       </c>
       <c r="W72">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>4.045295469367739</v>
+        <v>3.760601399044614</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1255522296514189</v>
+        <v>0.1255672433977575</v>
       </c>
       <c r="C73">
-        <v>3.328148023681149</v>
+        <v>3.226755416402916</v>
       </c>
       <c r="D73">
-        <v>9.162348023681149</v>
+        <v>9.161155416402917</v>
       </c>
       <c r="E73">
-        <v>1.834199999999999</v>
+        <v>1.934399999999999</v>
       </c>
       <c r="F73">
-        <v>7.114199999999999</v>
+        <v>7.214399999999999</v>
       </c>
       <c r="G73">
         <v>1.28</v>
@@ -7267,28 +7267,28 @@
         <v>1.64</v>
       </c>
       <c r="M73">
-        <v>0.43610046</v>
+        <v>0.44224272</v>
       </c>
       <c r="N73">
-        <v>1.20389954</v>
+        <v>1.19775728</v>
       </c>
       <c r="O73">
-        <v>0.120389954</v>
+        <v>0.119775728</v>
       </c>
       <c r="P73">
-        <v>1.083509586</v>
+        <v>1.077981552</v>
       </c>
       <c r="Q73">
-        <v>2.453509586</v>
+        <v>2.447981552</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2978673436255825</v>
+        <v>0.3065887264205626</v>
       </c>
       <c r="T73">
-        <v>3.899401638866084</v>
+        <v>4.034318656972322</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.760601399044614</v>
+        <v>3.708370824057884</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1255672433977575</v>
+        <v>0.1255822571440962</v>
       </c>
       <c r="C74">
-        <v>3.226755416402916</v>
+        <v>3.125363119553193</v>
       </c>
       <c r="D74">
-        <v>9.161155416402917</v>
+        <v>9.159963119553193</v>
       </c>
       <c r="E74">
-        <v>1.934399999999999</v>
+        <v>2.034599999999999</v>
       </c>
       <c r="F74">
-        <v>7.214399999999999</v>
+        <v>7.3146</v>
       </c>
       <c r="G74">
         <v>1.28</v>
@@ -7349,28 +7349,28 @@
         <v>1.64</v>
       </c>
       <c r="M74">
-        <v>0.44224272</v>
+        <v>0.44838498</v>
       </c>
       <c r="N74">
-        <v>1.19775728</v>
+        <v>1.19161502</v>
       </c>
       <c r="O74">
-        <v>0.119775728</v>
+        <v>0.119161502</v>
       </c>
       <c r="P74">
-        <v>1.077981552</v>
+        <v>1.072453518</v>
       </c>
       <c r="Q74">
-        <v>2.447981552</v>
+        <v>2.442453518</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3065887264205626</v>
+        <v>0.3159561375707265</v>
       </c>
       <c r="T74">
-        <v>4.034318656972322</v>
+        <v>4.179229528271615</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.708370824057884</v>
+        <v>3.657571223728323</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1255822571440962</v>
+        <v>0.1255972708904348</v>
       </c>
       <c r="C75">
-        <v>3.125363119553193</v>
+        <v>3.023971133010784</v>
       </c>
       <c r="D75">
-        <v>9.159963119553193</v>
+        <v>9.158771133010784</v>
       </c>
       <c r="E75">
-        <v>2.034599999999999</v>
+        <v>2.134799999999999</v>
       </c>
       <c r="F75">
-        <v>7.3146</v>
+        <v>7.4148</v>
       </c>
       <c r="G75">
         <v>1.28</v>
@@ -7431,28 +7431,28 @@
         <v>1.64</v>
       </c>
       <c r="M75">
-        <v>0.44838498</v>
+        <v>0.45452724</v>
       </c>
       <c r="N75">
-        <v>1.19161502</v>
+        <v>1.18547276</v>
       </c>
       <c r="O75">
-        <v>0.119161502</v>
+        <v>0.118547276</v>
       </c>
       <c r="P75">
-        <v>1.072453518</v>
+        <v>1.066925484</v>
       </c>
       <c r="Q75">
-        <v>2.442453518</v>
+        <v>2.436925484</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3159561375707265</v>
+        <v>0.3260441188093645</v>
       </c>
       <c r="T75">
-        <v>4.179229528271615</v>
+        <v>4.335287389670854</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.657571223728323</v>
+        <v>3.608144585569832</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1255972708904348</v>
+        <v>0.1256122846367734</v>
       </c>
       <c r="C76">
-        <v>3.023971133010784</v>
+        <v>2.92257945665457</v>
       </c>
       <c r="D76">
-        <v>9.158771133010784</v>
+        <v>9.15757945665457</v>
       </c>
       <c r="E76">
-        <v>2.134799999999999</v>
+        <v>2.234999999999999</v>
       </c>
       <c r="F76">
-        <v>7.4148</v>
+        <v>7.515</v>
       </c>
       <c r="G76">
         <v>1.28</v>
@@ -7513,28 +7513,28 @@
         <v>1.64</v>
       </c>
       <c r="M76">
-        <v>0.45452724</v>
+        <v>0.4606695</v>
       </c>
       <c r="N76">
-        <v>1.18547276</v>
+        <v>1.1793305</v>
       </c>
       <c r="O76">
-        <v>0.118547276</v>
+        <v>0.11793305</v>
       </c>
       <c r="P76">
-        <v>1.066925484</v>
+        <v>1.06139745</v>
       </c>
       <c r="Q76">
-        <v>2.436925484</v>
+        <v>2.43139745</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3260441188093645</v>
+        <v>0.3369391385470937</v>
       </c>
       <c r="T76">
-        <v>4.335287389670854</v>
+        <v>4.503829879982033</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.608144585569832</v>
+        <v>3.560035991095567</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1256122846367734</v>
+        <v>0.125627298383112</v>
       </c>
       <c r="C77">
-        <v>2.92257945665457</v>
+        <v>2.821188090363488</v>
       </c>
       <c r="D77">
-        <v>9.15757945665457</v>
+        <v>9.156388090363489</v>
       </c>
       <c r="E77">
-        <v>2.234999999999999</v>
+        <v>2.335199999999999</v>
       </c>
       <c r="F77">
-        <v>7.515</v>
+        <v>7.6152</v>
       </c>
       <c r="G77">
         <v>1.28</v>
@@ -7595,28 +7595,28 @@
         <v>1.64</v>
       </c>
       <c r="M77">
-        <v>0.4606695</v>
+        <v>0.46681176</v>
       </c>
       <c r="N77">
-        <v>1.1793305</v>
+        <v>1.17318824</v>
       </c>
       <c r="O77">
-        <v>0.11793305</v>
+        <v>0.117318824</v>
       </c>
       <c r="P77">
-        <v>1.06139745</v>
+        <v>1.055869416</v>
       </c>
       <c r="Q77">
-        <v>2.43139745</v>
+        <v>2.425869416</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3369391385470937</v>
+        <v>0.3487420765963002</v>
       </c>
       <c r="T77">
-        <v>4.503829879982033</v>
+        <v>4.686417577819142</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.560035991095567</v>
+        <v>3.513193412265363</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.125627298383112</v>
+        <v>0.1275827121294507</v>
       </c>
       <c r="C78">
-        <v>2.821188090363488</v>
+        <v>2.5684278428457</v>
       </c>
       <c r="D78">
-        <v>9.156388090363489</v>
+        <v>9.0038278428457</v>
       </c>
       <c r="E78">
-        <v>2.335199999999999</v>
+        <v>2.4354</v>
       </c>
       <c r="F78">
-        <v>7.6152</v>
+        <v>7.7154</v>
       </c>
       <c r="G78">
         <v>1.28</v>
@@ -7677,45 +7677,45 @@
         <v>1.64</v>
       </c>
       <c r="M78">
-        <v>0.46681176</v>
+        <v>0.49455714</v>
       </c>
       <c r="N78">
-        <v>1.17318824</v>
+        <v>1.14544286</v>
       </c>
       <c r="O78">
-        <v>0.117318824</v>
+        <v>0.114544286</v>
       </c>
       <c r="P78">
-        <v>1.055869416</v>
+        <v>1.030898574</v>
       </c>
       <c r="Q78">
-        <v>2.425869416</v>
+        <v>2.400898574</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3487420765963002</v>
+        <v>0.3615713570845681</v>
       </c>
       <c r="T78">
-        <v>4.686417577819142</v>
+        <v>4.884882466772522</v>
       </c>
       <c r="U78">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V78">
         <v>0.1</v>
       </c>
       <c r="W78">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>3.513193412265363</v>
+        <v>3.316098115578717</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1275827121294507</v>
+        <v>0.1276229258757893</v>
       </c>
       <c r="C79">
-        <v>2.5684278428457</v>
+        <v>2.465143721485051</v>
       </c>
       <c r="D79">
-        <v>9.0038278428457</v>
+        <v>9.000743721485051</v>
       </c>
       <c r="E79">
-        <v>2.4354</v>
+        <v>2.5356</v>
       </c>
       <c r="F79">
-        <v>7.7154</v>
+        <v>7.8156</v>
       </c>
       <c r="G79">
         <v>1.28</v>
@@ -7759,28 +7759,28 @@
         <v>1.64</v>
       </c>
       <c r="M79">
-        <v>0.49455714</v>
+        <v>0.50097996</v>
       </c>
       <c r="N79">
-        <v>1.14544286</v>
+        <v>1.13902004</v>
       </c>
       <c r="O79">
-        <v>0.114544286</v>
+        <v>0.113902004</v>
       </c>
       <c r="P79">
-        <v>1.030898574</v>
+        <v>1.025118036</v>
       </c>
       <c r="Q79">
-        <v>2.400898574</v>
+        <v>2.395118036</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3615713570845681</v>
+        <v>0.3755669357990422</v>
       </c>
       <c r="T79">
-        <v>4.884882466772522</v>
+        <v>5.101389618358027</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.316098115578717</v>
+        <v>3.273584037173861</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1276229258757893</v>
+        <v>0.1276631396221279</v>
       </c>
       <c r="C80">
-        <v>2.465143721485051</v>
+        <v>2.361861712236654</v>
       </c>
       <c r="D80">
-        <v>9.000743721485051</v>
+        <v>8.997661712236654</v>
       </c>
       <c r="E80">
-        <v>2.5356</v>
+        <v>2.6358</v>
       </c>
       <c r="F80">
-        <v>7.8156</v>
+        <v>7.9158</v>
       </c>
       <c r="G80">
         <v>1.28</v>
@@ -7841,28 +7841,28 @@
         <v>1.64</v>
       </c>
       <c r="M80">
-        <v>0.50097996</v>
+        <v>0.5074027800000001</v>
       </c>
       <c r="N80">
-        <v>1.13902004</v>
+        <v>1.13259722</v>
       </c>
       <c r="O80">
-        <v>0.113902004</v>
+        <v>0.113259722</v>
       </c>
       <c r="P80">
-        <v>1.025118036</v>
+        <v>1.019337498</v>
       </c>
       <c r="Q80">
-        <v>2.395118036</v>
+        <v>2.389337498</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3755669357990422</v>
+        <v>0.3908954267720376</v>
       </c>
       <c r="T80">
-        <v>5.101389618358027</v>
+        <v>5.338516498665961</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.273584037173861</v>
+        <v>3.232146264551407</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1276631396221279</v>
+        <v>0.1277033533684665</v>
       </c>
       <c r="C81">
-        <v>2.361861712236654</v>
+        <v>2.258581812931581</v>
       </c>
       <c r="D81">
-        <v>8.997661712236654</v>
+        <v>8.994581812931582</v>
       </c>
       <c r="E81">
-        <v>2.6358</v>
+        <v>2.736</v>
       </c>
       <c r="F81">
-        <v>7.9158</v>
+        <v>8.016</v>
       </c>
       <c r="G81">
         <v>1.28</v>
@@ -7923,28 +7923,28 @@
         <v>1.64</v>
       </c>
       <c r="M81">
-        <v>0.5074027800000001</v>
+        <v>0.5138256</v>
       </c>
       <c r="N81">
-        <v>1.13259722</v>
+        <v>1.1261744</v>
       </c>
       <c r="O81">
-        <v>0.113259722</v>
+        <v>0.11261744</v>
       </c>
       <c r="P81">
-        <v>1.019337498</v>
+        <v>1.01355696</v>
       </c>
       <c r="Q81">
-        <v>2.389337498</v>
+        <v>2.38355696</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3908954267720376</v>
+        <v>0.4077567668423328</v>
       </c>
       <c r="T81">
-        <v>5.338516498665961</v>
+        <v>5.599356067004691</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.232146264551407</v>
+        <v>3.191744436244515</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1277033533684665</v>
+        <v>0.1277435671148051</v>
       </c>
       <c r="C82">
-        <v>2.258581812931581</v>
+        <v>2.155304021403877</v>
       </c>
       <c r="D82">
-        <v>8.994581812931582</v>
+        <v>8.991504021403879</v>
       </c>
       <c r="E82">
-        <v>2.736</v>
+        <v>2.836200000000001</v>
       </c>
       <c r="F82">
-        <v>8.016</v>
+        <v>8.116200000000001</v>
       </c>
       <c r="G82">
         <v>1.28</v>
@@ -8005,28 +8005,28 @@
         <v>1.64</v>
       </c>
       <c r="M82">
-        <v>0.5138256</v>
+        <v>0.52024842</v>
       </c>
       <c r="N82">
-        <v>1.1261744</v>
+        <v>1.11975158</v>
       </c>
       <c r="O82">
-        <v>0.11261744</v>
+        <v>0.111975158</v>
       </c>
       <c r="P82">
-        <v>1.01355696</v>
+        <v>1.007776422</v>
       </c>
       <c r="Q82">
-        <v>2.38355696</v>
+        <v>2.377776422</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4077567668423328</v>
+        <v>0.426392984814764</v>
       </c>
       <c r="T82">
-        <v>5.599356067004691</v>
+        <v>5.887652432010652</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.191744436244515</v>
+        <v>3.1523401839452</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1277435671148051</v>
+        <v>0.1277837808611438</v>
       </c>
       <c r="C83">
-        <v>2.155304021403877</v>
+        <v>2.052028335490546</v>
       </c>
       <c r="D83">
-        <v>8.991504021403879</v>
+        <v>8.988428335490546</v>
       </c>
       <c r="E83">
-        <v>2.836200000000001</v>
+        <v>2.9364</v>
       </c>
       <c r="F83">
-        <v>8.116200000000001</v>
+        <v>8.2164</v>
       </c>
       <c r="G83">
         <v>1.28</v>
@@ -8087,28 +8087,28 @@
         <v>1.64</v>
       </c>
       <c r="M83">
-        <v>0.52024842</v>
+        <v>0.5266712400000001</v>
       </c>
       <c r="N83">
-        <v>1.11975158</v>
+        <v>1.113328759999999</v>
       </c>
       <c r="O83">
-        <v>0.111975158</v>
+        <v>0.111332876</v>
       </c>
       <c r="P83">
-        <v>1.007776422</v>
+        <v>1.001995884</v>
       </c>
       <c r="Q83">
-        <v>2.377776422</v>
+        <v>2.371995883999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.426392984814764</v>
+        <v>0.4470998936730211</v>
       </c>
       <c r="T83">
-        <v>5.887652432010652</v>
+        <v>6.207981726461722</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.1523401839452</v>
+        <v>3.113897010970258</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1277837808611438</v>
+        <v>0.1278239946074824</v>
       </c>
       <c r="C84">
-        <v>2.052028335490546</v>
+        <v>1.948754753031551</v>
       </c>
       <c r="D84">
-        <v>8.988428335490546</v>
+        <v>8.985354753031553</v>
       </c>
       <c r="E84">
-        <v>2.9364</v>
+        <v>3.036600000000001</v>
       </c>
       <c r="F84">
-        <v>8.2164</v>
+        <v>8.316600000000001</v>
       </c>
       <c r="G84">
         <v>1.28</v>
@@ -8169,28 +8169,28 @@
         <v>1.64</v>
       </c>
       <c r="M84">
-        <v>0.5266712400000001</v>
+        <v>0.5330940600000001</v>
       </c>
       <c r="N84">
-        <v>1.113328759999999</v>
+        <v>1.106905939999999</v>
       </c>
       <c r="O84">
-        <v>0.111332876</v>
+        <v>0.1106905939999999</v>
       </c>
       <c r="P84">
-        <v>1.001995884</v>
+        <v>0.9962153459999995</v>
       </c>
       <c r="Q84">
-        <v>2.371995883999999</v>
+        <v>2.366215346</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4470998936730211</v>
+        <v>0.470242909455779</v>
       </c>
       <c r="T84">
-        <v>6.207981726461722</v>
+        <v>6.565996820259977</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.113897010970258</v>
+        <v>3.076380179512785</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1278239946074824</v>
+        <v>0.127864208353821</v>
       </c>
       <c r="C85">
-        <v>1.948754753031551</v>
+        <v>1.845483271869803</v>
       </c>
       <c r="D85">
-        <v>8.985354753031553</v>
+        <v>8.982283271869804</v>
       </c>
       <c r="E85">
-        <v>3.036600000000001</v>
+        <v>3.1368</v>
       </c>
       <c r="F85">
-        <v>8.316600000000001</v>
+        <v>8.4168</v>
       </c>
       <c r="G85">
         <v>1.28</v>
@@ -8251,28 +8251,28 @@
         <v>1.64</v>
       </c>
       <c r="M85">
-        <v>0.5330940600000001</v>
+        <v>0.5395168800000001</v>
       </c>
       <c r="N85">
-        <v>1.106905939999999</v>
+        <v>1.10048312</v>
       </c>
       <c r="O85">
-        <v>0.1106905939999999</v>
+        <v>0.110048312</v>
       </c>
       <c r="P85">
-        <v>0.9962153459999995</v>
+        <v>0.9904348079999996</v>
       </c>
       <c r="Q85">
-        <v>2.366215346</v>
+        <v>2.360434808</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.470242909455779</v>
+        <v>0.4962788022113817</v>
       </c>
       <c r="T85">
-        <v>6.565996820259977</v>
+        <v>6.968763800783013</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.076380179512785</v>
+        <v>3.039756605947157</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.127864208353821</v>
+        <v>0.1279044221001596</v>
       </c>
       <c r="C86">
-        <v>1.845483271869805</v>
+        <v>1.742213889851177</v>
       </c>
       <c r="D86">
-        <v>8.982283271869804</v>
+        <v>8.979213889851177</v>
       </c>
       <c r="E86">
-        <v>3.136799999999998</v>
+        <v>3.236999999999999</v>
       </c>
       <c r="F86">
-        <v>8.416799999999999</v>
+        <v>8.516999999999999</v>
       </c>
       <c r="G86">
         <v>1.28</v>
@@ -8333,28 +8333,28 @@
         <v>1.64</v>
       </c>
       <c r="M86">
-        <v>0.53951688</v>
+        <v>0.5459397</v>
       </c>
       <c r="N86">
-        <v>1.10048312</v>
+        <v>1.0940603</v>
       </c>
       <c r="O86">
-        <v>0.110048312</v>
+        <v>0.10940603</v>
       </c>
       <c r="P86">
-        <v>0.9904348079999998</v>
+        <v>0.9846542699999998</v>
       </c>
       <c r="Q86">
-        <v>2.360434808</v>
+        <v>2.35465427</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4962788022113813</v>
+        <v>0.5257861473343975</v>
       </c>
       <c r="T86">
-        <v>6.968763800783009</v>
+        <v>7.425233045375783</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.039756605947157</v>
+        <v>3.00399476352425</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1279044221001596</v>
+        <v>0.1339818358464983</v>
       </c>
       <c r="C87">
-        <v>1.742213889851177</v>
+        <v>1.201074805801886</v>
       </c>
       <c r="D87">
-        <v>8.979213889851177</v>
+        <v>8.538274805801885</v>
       </c>
       <c r="E87">
-        <v>3.236999999999999</v>
+        <v>3.337199999999998</v>
       </c>
       <c r="F87">
-        <v>8.516999999999999</v>
+        <v>8.617199999999999</v>
       </c>
       <c r="G87">
         <v>1.28</v>
@@ -8415,45 +8415,45 @@
         <v>1.64</v>
       </c>
       <c r="M87">
-        <v>0.5459397</v>
+        <v>0.61957668</v>
       </c>
       <c r="N87">
-        <v>1.0940603</v>
+        <v>1.02042332</v>
       </c>
       <c r="O87">
-        <v>0.10940603</v>
+        <v>0.102042332</v>
       </c>
       <c r="P87">
-        <v>0.9846542699999998</v>
+        <v>0.9183809879999997</v>
       </c>
       <c r="Q87">
-        <v>2.35465427</v>
+        <v>2.288380988</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5257861473343975</v>
+        <v>0.5595088274749875</v>
       </c>
       <c r="T87">
-        <v>7.425233045375783</v>
+        <v>7.946912182053238</v>
       </c>
       <c r="U87">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V87">
         <v>0.1</v>
       </c>
       <c r="W87">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y87">
-        <v>3.00399476352425</v>
+        <v>2.646968572154781</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1339818358464983</v>
+        <v>0.1340922495928369</v>
       </c>
       <c r="C88">
-        <v>1.201074805801886</v>
+        <v>1.093264055735535</v>
       </c>
       <c r="D88">
-        <v>8.538274805801885</v>
+        <v>8.530664055735535</v>
       </c>
       <c r="E88">
-        <v>3.337199999999998</v>
+        <v>3.437399999999999</v>
       </c>
       <c r="F88">
-        <v>8.617199999999999</v>
+        <v>8.7174</v>
       </c>
       <c r="G88">
         <v>1.28</v>
@@ -8497,28 +8497,28 @@
         <v>1.64</v>
       </c>
       <c r="M88">
-        <v>0.61957668</v>
+        <v>0.62678106</v>
       </c>
       <c r="N88">
-        <v>1.02042332</v>
+        <v>1.01321894</v>
       </c>
       <c r="O88">
-        <v>0.102042332</v>
+        <v>0.101321894</v>
       </c>
       <c r="P88">
-        <v>0.9183809879999997</v>
+        <v>0.9118970459999998</v>
       </c>
       <c r="Q88">
-        <v>2.288380988</v>
+        <v>2.281897046</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5595088274749875</v>
+        <v>0.5984196122525913</v>
       </c>
       <c r="T88">
-        <v>7.946912182053238</v>
+        <v>8.548849647450302</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.646968572154781</v>
+        <v>2.61654364603806</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1340922495928369</v>
+        <v>0.1342026633391755</v>
       </c>
       <c r="C89">
-        <v>1.093264055735535</v>
+        <v>0.985466861553169</v>
       </c>
       <c r="D89">
-        <v>8.530664055735535</v>
+        <v>8.52306686155317</v>
       </c>
       <c r="E89">
-        <v>3.437399999999999</v>
+        <v>3.5376</v>
       </c>
       <c r="F89">
-        <v>8.7174</v>
+        <v>8.817600000000001</v>
       </c>
       <c r="G89">
         <v>1.28</v>
@@ -8579,28 +8579,28 @@
         <v>1.64</v>
       </c>
       <c r="M89">
-        <v>0.62678106</v>
+        <v>0.6339854400000001</v>
       </c>
       <c r="N89">
-        <v>1.01321894</v>
+        <v>1.00601456</v>
       </c>
       <c r="O89">
-        <v>0.101321894</v>
+        <v>0.100601456</v>
       </c>
       <c r="P89">
-        <v>0.9118970459999998</v>
+        <v>0.9054131039999997</v>
       </c>
       <c r="Q89">
-        <v>2.281897046</v>
+        <v>2.275413104</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5984196122525913</v>
+        <v>0.6438155278264626</v>
       </c>
       <c r="T89">
-        <v>8.548849647450302</v>
+        <v>9.251110023746877</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.61654364603806</v>
+        <v>2.586810195514899</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1342026633391755</v>
+        <v>0.1343130770855141</v>
       </c>
       <c r="C90">
-        <v>0.985466861553169</v>
+        <v>0.877683187069433</v>
       </c>
       <c r="D90">
-        <v>8.52306686155317</v>
+        <v>8.515483187069433</v>
       </c>
       <c r="E90">
-        <v>3.5376</v>
+        <v>3.637799999999999</v>
       </c>
       <c r="F90">
-        <v>8.817600000000001</v>
+        <v>8.9178</v>
       </c>
       <c r="G90">
         <v>1.28</v>
@@ -8661,28 +8661,28 @@
         <v>1.64</v>
       </c>
       <c r="M90">
-        <v>0.6339854400000001</v>
+        <v>0.64118982</v>
       </c>
       <c r="N90">
-        <v>1.00601456</v>
+        <v>0.9988101799999997</v>
       </c>
       <c r="O90">
-        <v>0.100601456</v>
+        <v>0.09988101799999997</v>
       </c>
       <c r="P90">
-        <v>0.9054131039999997</v>
+        <v>0.8989291619999997</v>
       </c>
       <c r="Q90">
-        <v>2.275413104</v>
+        <v>2.268929162</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6438155278264626</v>
+        <v>0.6974652462319467</v>
       </c>
       <c r="T90">
-        <v>9.251110023746877</v>
+        <v>10.08105410482465</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.586810195514899</v>
+        <v>2.557744912419227</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1343130770855141</v>
+        <v>0.1344234908318528</v>
       </c>
       <c r="C91">
-        <v>0.877683187069433</v>
+        <v>0.7699129962276352</v>
       </c>
       <c r="D91">
-        <v>8.515483187069433</v>
+        <v>8.507912996227637</v>
       </c>
       <c r="E91">
-        <v>3.637799999999999</v>
+        <v>3.738</v>
       </c>
       <c r="F91">
-        <v>8.9178</v>
+        <v>9.018000000000001</v>
       </c>
       <c r="G91">
         <v>1.28</v>
@@ -8743,28 +8743,28 @@
         <v>1.64</v>
       </c>
       <c r="M91">
-        <v>0.64118982</v>
+        <v>0.6483942000000001</v>
       </c>
       <c r="N91">
-        <v>0.9988101799999997</v>
+        <v>0.9916057999999995</v>
       </c>
       <c r="O91">
-        <v>0.09988101799999997</v>
+        <v>0.09916057999999996</v>
       </c>
       <c r="P91">
-        <v>0.8989291619999997</v>
+        <v>0.8924452199999996</v>
       </c>
       <c r="Q91">
-        <v>2.268929162</v>
+        <v>2.26244522</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6974652462319467</v>
+        <v>0.7618449083185276</v>
       </c>
       <c r="T91">
-        <v>10.08105410482465</v>
+        <v>11.07698700211797</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.557744912419227</v>
+        <v>2.529325524503457</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1344234908318528</v>
+        <v>0.1345339045781914</v>
       </c>
       <c r="C92">
-        <v>0.7699129962276352</v>
+        <v>0.6621562530991962</v>
       </c>
       <c r="D92">
-        <v>8.507912996227637</v>
+        <v>8.500356253099197</v>
       </c>
       <c r="E92">
-        <v>3.738</v>
+        <v>3.8382</v>
       </c>
       <c r="F92">
-        <v>9.018000000000001</v>
+        <v>9.1182</v>
       </c>
       <c r="G92">
         <v>1.28</v>
@@ -8825,28 +8825,28 @@
         <v>1.64</v>
       </c>
       <c r="M92">
-        <v>0.6483942000000001</v>
+        <v>0.65559858</v>
       </c>
       <c r="N92">
-        <v>0.9916057999999995</v>
+        <v>0.9844014199999996</v>
       </c>
       <c r="O92">
-        <v>0.09916057999999996</v>
+        <v>0.09844014199999997</v>
       </c>
       <c r="P92">
-        <v>0.8924452199999996</v>
+        <v>0.8859612779999997</v>
       </c>
       <c r="Q92">
-        <v>2.26244522</v>
+        <v>2.255961278</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7618449083185276</v>
+        <v>0.8405311619799045</v>
       </c>
       <c r="T92">
-        <v>11.07698700211797</v>
+        <v>12.29423832103204</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.529325524503457</v>
+        <v>2.501530738519903</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1345339045781914</v>
+        <v>0.13787351832453</v>
       </c>
       <c r="C93">
-        <v>0.6621562530991962</v>
+        <v>0.339569688591892</v>
       </c>
       <c r="D93">
-        <v>8.500356253099197</v>
+        <v>8.277969688591893</v>
       </c>
       <c r="E93">
-        <v>3.8382</v>
+        <v>3.938400000000001</v>
       </c>
       <c r="F93">
-        <v>9.1182</v>
+        <v>9.218400000000001</v>
       </c>
       <c r="G93">
         <v>1.28</v>
@@ -8907,45 +8907,45 @@
         <v>1.64</v>
       </c>
       <c r="M93">
-        <v>0.65559858</v>
+        <v>0.6987547200000002</v>
       </c>
       <c r="N93">
-        <v>0.9844014199999996</v>
+        <v>0.9412452799999995</v>
       </c>
       <c r="O93">
-        <v>0.09844014199999997</v>
+        <v>0.09412452799999996</v>
       </c>
       <c r="P93">
-        <v>0.8859612779999997</v>
+        <v>0.8471207519999996</v>
       </c>
       <c r="Q93">
-        <v>2.255961278</v>
+        <v>2.217120752</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8405311619799045</v>
+        <v>0.9388889790566256</v>
       </c>
       <c r="T93">
-        <v>12.29423832103204</v>
+        <v>13.81580246967462</v>
       </c>
       <c r="U93">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V93">
         <v>0.1</v>
       </c>
       <c r="W93">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.501530738519903</v>
+        <v>2.347032446521434</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.13787351832453</v>
+        <v>0.1380190320708686</v>
       </c>
       <c r="C94">
-        <v>0.339569688591892</v>
+        <v>0.2299441050390101</v>
       </c>
       <c r="D94">
-        <v>8.277969688591893</v>
+        <v>8.268544105039011</v>
       </c>
       <c r="E94">
-        <v>3.938400000000001</v>
+        <v>4.0386</v>
       </c>
       <c r="F94">
-        <v>9.218400000000001</v>
+        <v>9.3186</v>
       </c>
       <c r="G94">
         <v>1.28</v>
@@ -8989,28 +8989,28 @@
         <v>1.64</v>
       </c>
       <c r="M94">
-        <v>0.6987547200000002</v>
+        <v>0.7063498800000001</v>
       </c>
       <c r="N94">
-        <v>0.9412452799999995</v>
+        <v>0.9336501199999996</v>
       </c>
       <c r="O94">
-        <v>0.09412452799999996</v>
+        <v>0.09336501199999997</v>
       </c>
       <c r="P94">
-        <v>0.8471207519999996</v>
+        <v>0.8402851079999996</v>
       </c>
       <c r="Q94">
-        <v>2.217120752</v>
+        <v>2.210285108</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9388889790566256</v>
+        <v>1.065349029583838</v>
       </c>
       <c r="T94">
-        <v>13.81580246967462</v>
+        <v>15.77209923221508</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.347032446521434</v>
+        <v>2.321795538494322</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1380190320708686</v>
+        <v>0.1381645458172073</v>
       </c>
       <c r="C95">
-        <v>0.2299441050390101</v>
+        <v>0.1203399616666392</v>
       </c>
       <c r="D95">
-        <v>8.268544105039011</v>
+        <v>8.259139961666641</v>
       </c>
       <c r="E95">
-        <v>4.0386</v>
+        <v>4.138800000000001</v>
       </c>
       <c r="F95">
-        <v>9.3186</v>
+        <v>9.418800000000001</v>
       </c>
       <c r="G95">
         <v>1.28</v>
@@ -9071,28 +9071,28 @@
         <v>1.64</v>
       </c>
       <c r="M95">
-        <v>0.7063498800000001</v>
+        <v>0.7139450400000001</v>
       </c>
       <c r="N95">
-        <v>0.9336501199999996</v>
+        <v>0.9260549599999995</v>
       </c>
       <c r="O95">
-        <v>0.09336501199999997</v>
+        <v>0.09260549599999995</v>
       </c>
       <c r="P95">
-        <v>0.8402851079999996</v>
+        <v>0.8334494639999996</v>
       </c>
       <c r="Q95">
-        <v>2.210285108</v>
+        <v>2.203449464</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.065349029583838</v>
+        <v>1.233962430286789</v>
       </c>
       <c r="T95">
-        <v>15.77209923221508</v>
+        <v>18.38049491560237</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.321795538494322</v>
+        <v>2.297095585957148</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1381645458172073</v>
+        <v>0.1383100595635459</v>
       </c>
       <c r="C96">
-        <v>0.1203399616666392</v>
+        <v>0.0107571854035875</v>
       </c>
       <c r="D96">
-        <v>8.259139961666641</v>
+        <v>8.249757185403588</v>
       </c>
       <c r="E96">
-        <v>4.138800000000001</v>
+        <v>4.239</v>
       </c>
       <c r="F96">
-        <v>9.418800000000001</v>
+        <v>9.519</v>
       </c>
       <c r="G96">
         <v>1.28</v>
@@ -9153,28 +9153,28 @@
         <v>1.64</v>
       </c>
       <c r="M96">
-        <v>0.7139450400000001</v>
+        <v>0.7215402000000001</v>
       </c>
       <c r="N96">
-        <v>0.9260549599999995</v>
+        <v>0.9184597999999996</v>
       </c>
       <c r="O96">
-        <v>0.09260549599999995</v>
+        <v>0.09184597999999997</v>
       </c>
       <c r="P96">
-        <v>0.8334494639999996</v>
+        <v>0.8266138199999996</v>
       </c>
       <c r="Q96">
-        <v>2.203449464</v>
+        <v>2.19661382</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.233962430286789</v>
+        <v>1.47002119127092</v>
       </c>
       <c r="T96">
-        <v>18.38049491560237</v>
+        <v>22.03224887234457</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.297095585957148</v>
+        <v>2.272915632420757</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1383100595635459</v>
+        <v>0.1384555733098845</v>
       </c>
       <c r="C97">
-        <v>0.0107571854035875</v>
+        <v>-0.09880429648967493</v>
       </c>
       <c r="D97">
-        <v>8.249757185403588</v>
+        <v>8.240395703510327</v>
       </c>
       <c r="E97">
-        <v>4.239</v>
+        <v>4.339200000000001</v>
       </c>
       <c r="F97">
-        <v>9.519</v>
+        <v>9.619200000000001</v>
       </c>
       <c r="G97">
         <v>1.28</v>
@@ -9235,28 +9235,28 @@
         <v>1.64</v>
       </c>
       <c r="M97">
-        <v>0.7215402000000001</v>
+        <v>0.7291353600000001</v>
       </c>
       <c r="N97">
-        <v>0.9184597999999996</v>
+        <v>0.9108646399999996</v>
       </c>
       <c r="O97">
-        <v>0.09184597999999997</v>
+        <v>0.09108646399999996</v>
       </c>
       <c r="P97">
-        <v>0.8266138199999996</v>
+        <v>0.8197781759999996</v>
       </c>
       <c r="Q97">
-        <v>2.19661382</v>
+        <v>2.189778176</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.47002119127092</v>
+        <v>1.824109332747116</v>
       </c>
       <c r="T97">
-        <v>22.03224887234457</v>
+        <v>27.50987980745787</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.272915632420757</v>
+        <v>2.249239427916374</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1384555733098845</v>
+        <v>0.1386010870562231</v>
       </c>
       <c r="C98">
-        <v>-0.09880429648967315</v>
+        <v>-0.2083445564228779</v>
       </c>
       <c r="D98">
-        <v>8.240395703510327</v>
+        <v>8.231055443577121</v>
       </c>
       <c r="E98">
-        <v>4.339199999999999</v>
+        <v>4.439399999999998</v>
       </c>
       <c r="F98">
-        <v>9.619199999999999</v>
+        <v>9.719399999999998</v>
       </c>
       <c r="G98">
         <v>1.28</v>
@@ -9317,28 +9317,28 @@
         <v>1.64</v>
       </c>
       <c r="M98">
-        <v>0.72913536</v>
+        <v>0.7367305199999999</v>
       </c>
       <c r="N98">
-        <v>0.9108646399999997</v>
+        <v>0.9032694799999997</v>
       </c>
       <c r="O98">
-        <v>0.09108646399999998</v>
+        <v>0.09032694799999998</v>
       </c>
       <c r="P98">
-        <v>0.8197781759999997</v>
+        <v>0.8129425319999998</v>
       </c>
       <c r="Q98">
-        <v>2.189778176</v>
+        <v>2.182942532</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.824109332747111</v>
+        <v>2.414256235207435</v>
       </c>
       <c r="T98">
-        <v>27.5098798074578</v>
+        <v>36.63926469931326</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.249239427916375</v>
+        <v>2.22605139257703</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1386010870562231</v>
+        <v>0.1387466008025617</v>
       </c>
       <c r="C99">
-        <v>-0.2083445564228779</v>
+        <v>-0.3178636664778267</v>
       </c>
       <c r="D99">
-        <v>8.231055443577121</v>
+        <v>8.221736333522173</v>
       </c>
       <c r="E99">
-        <v>4.439399999999998</v>
+        <v>4.539599999999999</v>
       </c>
       <c r="F99">
-        <v>9.719399999999998</v>
+        <v>9.819599999999999</v>
       </c>
       <c r="G99">
         <v>1.28</v>
@@ -9399,28 +9399,28 @@
         <v>1.64</v>
       </c>
       <c r="M99">
-        <v>0.7367305199999999</v>
+        <v>0.74432568</v>
       </c>
       <c r="N99">
-        <v>0.9032694799999997</v>
+        <v>0.8956743199999997</v>
       </c>
       <c r="O99">
-        <v>0.09032694799999998</v>
+        <v>0.08956743199999997</v>
       </c>
       <c r="P99">
-        <v>0.8129425319999998</v>
+        <v>0.8061068879999997</v>
       </c>
       <c r="Q99">
-        <v>2.182942532</v>
+        <v>2.176106888</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.414256235207435</v>
+        <v>3.594550040128084</v>
       </c>
       <c r="T99">
-        <v>36.63926469931326</v>
+        <v>54.89803448302419</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.22605139257703</v>
+        <v>2.203336582448693</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1387466008025617</v>
+        <v>0.1388921145489004</v>
       </c>
       <c r="C100">
-        <v>-0.3178636664778267</v>
+        <v>-0.4273616984102606</v>
       </c>
       <c r="D100">
-        <v>8.221736333522173</v>
+        <v>8.212438301589739</v>
       </c>
       <c r="E100">
-        <v>4.539599999999999</v>
+        <v>4.639799999999998</v>
       </c>
       <c r="F100">
-        <v>9.819599999999999</v>
+        <v>9.919799999999999</v>
       </c>
       <c r="G100">
         <v>1.28</v>
@@ -9481,28 +9481,28 @@
         <v>1.64</v>
       </c>
       <c r="M100">
-        <v>0.74432568</v>
+        <v>0.7519208399999999</v>
       </c>
       <c r="N100">
-        <v>0.8956743199999997</v>
+        <v>0.8880791599999998</v>
       </c>
       <c r="O100">
-        <v>0.08956743199999997</v>
+        <v>0.08880791599999999</v>
       </c>
       <c r="P100">
-        <v>0.8061068879999997</v>
+        <v>0.7992712439999998</v>
       </c>
       <c r="Q100">
-        <v>2.176106888</v>
+        <v>2.169271244</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.594550040128084</v>
+        <v>7.135431454890031</v>
       </c>
       <c r="T100">
-        <v>54.89803448302419</v>
+        <v>109.674343834157</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.203336582448693</v>
+        <v>2.181080657373454</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1388921145489004</v>
-      </c>
-      <c r="C101">
-        <v>-0.4273616984102606</v>
-      </c>
-      <c r="D101">
-        <v>8.212438301589739</v>
-      </c>
-      <c r="E101">
-        <v>4.639799999999998</v>
-      </c>
-      <c r="F101">
-        <v>9.919799999999999</v>
-      </c>
-      <c r="G101">
-        <v>1.28</v>
-      </c>
-      <c r="H101">
-        <v>4.74</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.01</v>
-      </c>
-      <c r="K101">
-        <v>1.37</v>
-      </c>
-      <c r="L101">
-        <v>1.64</v>
-      </c>
-      <c r="M101">
-        <v>0.7519208399999999</v>
-      </c>
-      <c r="N101">
-        <v>0.8880791599999998</v>
-      </c>
-      <c r="O101">
-        <v>0.08880791599999999</v>
-      </c>
-      <c r="P101">
-        <v>0.7992712439999998</v>
-      </c>
-      <c r="Q101">
-        <v>2.169271244</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.135431454890031</v>
-      </c>
-      <c r="T101">
-        <v>109.674343834157</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.1</v>
-      </c>
-      <c r="W101">
-        <v>0.06822</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.181080657373454</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
